--- a/dist/Wedding-Planner-All-In-One.xlsx
+++ b/dist/Wedding-Planner-All-In-One.xlsx
@@ -6819,11 +6819,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="98346222"/>
-        <c:axId val="95598873"/>
+        <c:axId val="72130385"/>
+        <c:axId val="18722873"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="98346222"/>
+        <c:axId val="72130385"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6855,7 +6855,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="95598873"/>
+        <c:crossAx val="18722873"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6863,7 +6863,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="95598873"/>
+        <c:axId val="18722873"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6895,7 +6895,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="98346222"/>
+        <c:crossAx val="72130385"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7582,11 +7582,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="54052013"/>
-        <c:axId val="6349449"/>
+        <c:axId val="39179791"/>
+        <c:axId val="94226096"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="54052013"/>
+        <c:axId val="39179791"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7618,7 +7618,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="6349449"/>
+        <c:crossAx val="94226096"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7626,7 +7626,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="6349449"/>
+        <c:axId val="94226096"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7658,7 +7658,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="54052013"/>
+        <c:crossAx val="39179791"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7830,11 +7830,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="55515679"/>
-        <c:axId val="79331679"/>
+        <c:axId val="80024276"/>
+        <c:axId val="50846560"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="55515679"/>
+        <c:axId val="80024276"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7866,7 +7866,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79331679"/>
+        <c:crossAx val="50846560"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7874,7 +7874,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="79331679"/>
+        <c:axId val="50846560"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7906,7 +7906,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="55515679"/>
+        <c:crossAx val="80024276"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8096,11 +8096,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="36518614"/>
-        <c:axId val="25591665"/>
+        <c:axId val="95051354"/>
+        <c:axId val="18957805"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="36518614"/>
+        <c:axId val="95051354"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8132,7 +8132,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="25591665"/>
+        <c:crossAx val="18957805"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8140,7 +8140,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="25591665"/>
+        <c:axId val="18957805"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8172,7 +8172,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="36518614"/>
+        <c:crossAx val="95051354"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8356,11 +8356,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="71393992"/>
-        <c:axId val="36504421"/>
+        <c:axId val="24199499"/>
+        <c:axId val="94282676"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="71393992"/>
+        <c:axId val="24199499"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8392,7 +8392,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="36504421"/>
+        <c:crossAx val="94282676"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8400,7 +8400,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="36504421"/>
+        <c:axId val="94282676"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8432,7 +8432,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="71393992"/>
+        <c:crossAx val="24199499"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8586,11 +8586,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="94526433"/>
-        <c:axId val="6871880"/>
+        <c:axId val="49601498"/>
+        <c:axId val="31837570"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="94526433"/>
+        <c:axId val="49601498"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8622,7 +8622,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="6871880"/>
+        <c:crossAx val="31837570"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8630,7 +8630,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="6871880"/>
+        <c:axId val="31837570"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8662,7 +8662,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94526433"/>
+        <c:crossAx val="49601498"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8822,11 +8822,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="50024369"/>
-        <c:axId val="56978632"/>
+        <c:axId val="14675865"/>
+        <c:axId val="87810862"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="50024369"/>
+        <c:axId val="14675865"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8858,7 +8858,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="56978632"/>
+        <c:crossAx val="87810862"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8866,7 +8866,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="56978632"/>
+        <c:axId val="87810862"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8898,7 +8898,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="50024369"/>
+        <c:crossAx val="14675865"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11375,11 +11375,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="36592648"/>
-        <c:axId val="31244834"/>
+        <c:axId val="86993302"/>
+        <c:axId val="41499633"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="36592648"/>
+        <c:axId val="86993302"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11411,7 +11411,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="31244834"/>
+        <c:crossAx val="41499633"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11419,7 +11419,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="31244834"/>
+        <c:axId val="41499633"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11451,7 +11451,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="36592648"/>
+        <c:crossAx val="86993302"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11866,11 +11866,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="75201424"/>
-        <c:axId val="44236749"/>
+        <c:axId val="67305794"/>
+        <c:axId val="60145589"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="75201424"/>
+        <c:axId val="67305794"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11902,7 +11902,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="44236749"/>
+        <c:crossAx val="60145589"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11910,7 +11910,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="44236749"/>
+        <c:axId val="60145589"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11942,7 +11942,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="75201424"/>
+        <c:crossAx val="67305794"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12474,11 +12474,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="68003451"/>
-        <c:axId val="44454610"/>
+        <c:axId val="61555467"/>
+        <c:axId val="80119946"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="68003451"/>
+        <c:axId val="61555467"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12510,7 +12510,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="44454610"/>
+        <c:crossAx val="80119946"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -12518,7 +12518,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="44454610"/>
+        <c:axId val="80119946"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12550,7 +12550,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="68003451"/>
+        <c:crossAx val="61555467"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12898,11 +12898,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="86859151"/>
-        <c:axId val="37287007"/>
+        <c:axId val="4239967"/>
+        <c:axId val="4923004"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="86859151"/>
+        <c:axId val="4239967"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12934,7 +12934,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37287007"/>
+        <c:crossAx val="4923004"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -12942,7 +12942,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="37287007"/>
+        <c:axId val="4923004"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12974,7 +12974,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="86859151"/>
+        <c:crossAx val="4239967"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13206,11 +13206,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="74801723"/>
-        <c:axId val="38012479"/>
+        <c:axId val="99395440"/>
+        <c:axId val="72770285"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="74801723"/>
+        <c:axId val="99395440"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13242,7 +13242,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="38012479"/>
+        <c:crossAx val="72770285"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -13250,7 +13250,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="38012479"/>
+        <c:axId val="72770285"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13282,7 +13282,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74801723"/>
+        <c:crossAx val="99395440"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14159,11 +14159,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="5375510"/>
-        <c:axId val="35382992"/>
+        <c:axId val="44891372"/>
+        <c:axId val="7335932"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="5375510"/>
+        <c:axId val="44891372"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14195,7 +14195,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="35382992"/>
+        <c:crossAx val="7335932"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -14203,7 +14203,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="35382992"/>
+        <c:axId val="7335932"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14235,7 +14235,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="5375510"/>
+        <c:crossAx val="44891372"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/dist/Wedding-Planner-All-In-One.xlsx
+++ b/dist/Wedding-Planner-All-In-One.xlsx
@@ -6819,11 +6819,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="72130385"/>
-        <c:axId val="18722873"/>
+        <c:axId val="82956033"/>
+        <c:axId val="57581551"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="72130385"/>
+        <c:axId val="82956033"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6855,7 +6855,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="18722873"/>
+        <c:crossAx val="57581551"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6863,7 +6863,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="18722873"/>
+        <c:axId val="57581551"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6895,7 +6895,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="72130385"/>
+        <c:crossAx val="82956033"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7582,11 +7582,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="39179791"/>
-        <c:axId val="94226096"/>
+        <c:axId val="66318600"/>
+        <c:axId val="88783639"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="39179791"/>
+        <c:axId val="66318600"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7618,7 +7618,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94226096"/>
+        <c:crossAx val="88783639"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7626,7 +7626,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="94226096"/>
+        <c:axId val="88783639"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7658,7 +7658,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="39179791"/>
+        <c:crossAx val="66318600"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7830,11 +7830,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="80024276"/>
-        <c:axId val="50846560"/>
+        <c:axId val="60487119"/>
+        <c:axId val="46071228"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="80024276"/>
+        <c:axId val="60487119"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7866,7 +7866,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="50846560"/>
+        <c:crossAx val="46071228"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7874,7 +7874,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="50846560"/>
+        <c:axId val="46071228"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7906,7 +7906,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80024276"/>
+        <c:crossAx val="60487119"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8096,11 +8096,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="95051354"/>
-        <c:axId val="18957805"/>
+        <c:axId val="71686446"/>
+        <c:axId val="80485631"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="95051354"/>
+        <c:axId val="71686446"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8132,7 +8132,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="18957805"/>
+        <c:crossAx val="80485631"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8140,7 +8140,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="18957805"/>
+        <c:axId val="80485631"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8172,7 +8172,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="95051354"/>
+        <c:crossAx val="71686446"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8356,11 +8356,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="24199499"/>
-        <c:axId val="94282676"/>
+        <c:axId val="9282771"/>
+        <c:axId val="37164128"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="24199499"/>
+        <c:axId val="9282771"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8392,7 +8392,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94282676"/>
+        <c:crossAx val="37164128"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8400,7 +8400,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="94282676"/>
+        <c:axId val="37164128"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8432,7 +8432,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="24199499"/>
+        <c:crossAx val="9282771"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8586,11 +8586,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="49601498"/>
-        <c:axId val="31837570"/>
+        <c:axId val="91602965"/>
+        <c:axId val="84366139"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="49601498"/>
+        <c:axId val="91602965"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8622,7 +8622,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="31837570"/>
+        <c:crossAx val="84366139"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8630,7 +8630,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="31837570"/>
+        <c:axId val="84366139"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8662,7 +8662,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="49601498"/>
+        <c:crossAx val="91602965"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8822,11 +8822,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="14675865"/>
-        <c:axId val="87810862"/>
+        <c:axId val="59003655"/>
+        <c:axId val="25491521"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="14675865"/>
+        <c:axId val="59003655"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8858,7 +8858,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="87810862"/>
+        <c:crossAx val="25491521"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8866,7 +8866,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="87810862"/>
+        <c:axId val="25491521"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8898,7 +8898,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="14675865"/>
+        <c:crossAx val="59003655"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11375,11 +11375,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="86993302"/>
-        <c:axId val="41499633"/>
+        <c:axId val="32516083"/>
+        <c:axId val="42938501"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="86993302"/>
+        <c:axId val="32516083"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11411,7 +11411,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="41499633"/>
+        <c:crossAx val="42938501"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11419,7 +11419,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="41499633"/>
+        <c:axId val="42938501"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11451,7 +11451,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="86993302"/>
+        <c:crossAx val="32516083"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11866,11 +11866,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="67305794"/>
-        <c:axId val="60145589"/>
+        <c:axId val="33366213"/>
+        <c:axId val="7906641"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="67305794"/>
+        <c:axId val="33366213"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11902,7 +11902,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="60145589"/>
+        <c:crossAx val="7906641"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11910,7 +11910,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="60145589"/>
+        <c:axId val="7906641"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11942,7 +11942,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67305794"/>
+        <c:crossAx val="33366213"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12474,11 +12474,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="61555467"/>
-        <c:axId val="80119946"/>
+        <c:axId val="9374041"/>
+        <c:axId val="94208852"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="61555467"/>
+        <c:axId val="9374041"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12510,7 +12510,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80119946"/>
+        <c:crossAx val="94208852"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -12518,7 +12518,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="80119946"/>
+        <c:axId val="94208852"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12550,7 +12550,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="61555467"/>
+        <c:crossAx val="9374041"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12898,11 +12898,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="4239967"/>
-        <c:axId val="4923004"/>
+        <c:axId val="25309719"/>
+        <c:axId val="30541203"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="4239967"/>
+        <c:axId val="25309719"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12934,7 +12934,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="4923004"/>
+        <c:crossAx val="30541203"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -12942,7 +12942,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="4923004"/>
+        <c:axId val="30541203"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12974,7 +12974,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="4239967"/>
+        <c:crossAx val="25309719"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13206,11 +13206,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="99395440"/>
-        <c:axId val="72770285"/>
+        <c:axId val="18936560"/>
+        <c:axId val="49144451"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="99395440"/>
+        <c:axId val="18936560"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13242,7 +13242,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="72770285"/>
+        <c:crossAx val="49144451"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -13250,7 +13250,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="72770285"/>
+        <c:axId val="49144451"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13282,7 +13282,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99395440"/>
+        <c:crossAx val="18936560"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14159,11 +14159,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="44891372"/>
-        <c:axId val="7335932"/>
+        <c:axId val="50772334"/>
+        <c:axId val="12516956"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="44891372"/>
+        <c:axId val="50772334"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14195,7 +14195,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="7335932"/>
+        <c:crossAx val="12516956"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -14203,7 +14203,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="7335932"/>
+        <c:axId val="12516956"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14235,7 +14235,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="44891372"/>
+        <c:crossAx val="50772334"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/dist/Wedding-Planner-All-In-One.xlsx
+++ b/dist/Wedding-Planner-All-In-One.xlsx
@@ -86,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7531" uniqueCount="1696">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7588" uniqueCount="1729">
   <si>
     <t xml:space="preserve">WELCOME TO YOUR WEDDING PLANNER</t>
   </si>
@@ -3949,6 +3949,12 @@
     <t xml:space="preserve">Venue 5</t>
   </si>
   <si>
+    <t xml:space="preserve">The Grand Hall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seaside Terrace</t>
+  </si>
+  <si>
     <t xml:space="preserve">Photo Placeholder</t>
   </si>
   <si>
@@ -3958,9 +3964,21 @@
     <t xml:space="preserve">Contact Info</t>
   </si>
   <si>
+    <t xml:space="preserve">555-0180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">555-0199</t>
+  </si>
+  <si>
     <t xml:space="preserve">Capacity</t>
   </si>
   <si>
+    <t xml:space="preserve">Available</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waitlist</t>
+  </si>
+  <si>
     <t xml:space="preserve">Venue Fee</t>
   </si>
   <si>
@@ -4594,6 +4612,39 @@
     <t xml:space="preserve">For Person / Role</t>
   </si>
   <si>
+    <t xml:space="preserve">Wedding Day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alterations booked for May</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trial done, loved it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navy three-piece, ordered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bridesmaids</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sage green, all sizes in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rental, pickup week before</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outfit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">White jumpsuit</t>
+  </si>
+  <si>
     <t xml:space="preserve">PHOTO REFERENCE GALLERY</t>
   </si>
   <si>
@@ -4648,6 +4699,60 @@
     <t xml:space="preserve">Pickup Time</t>
   </si>
   <si>
+    <t xml:space="preserve">Bridal Party</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elegant Limo Co.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">555-0200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bridal Suite Hotel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8-seater stretch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guest Shuttle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">City Coach Lines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">555-0210</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Downtown Hotel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two return trips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Family</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Family Home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grandparents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Couple Getaway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Classic Car Hire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">555-0220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Grand Hotel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vintage car</t>
+  </si>
+  <si>
     <t xml:space="preserve">WEDDING STATIONERY: CHECKLIST</t>
   </si>
   <si>
@@ -4705,9 +4810,6 @@
     <t xml:space="preserve">Not Ordered</t>
   </si>
   <si>
-    <t xml:space="preserve">Wedding Day</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ceremony Programs</t>
   </si>
   <si>
@@ -5033,9 +5135,6 @@
   </si>
   <si>
     <t xml:space="preserve">Low</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Family</t>
   </si>
   <si>
     <t xml:space="preserve">Grand Hotel</t>
@@ -6819,11 +6918,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="82956033"/>
-        <c:axId val="57581551"/>
+        <c:axId val="66932702"/>
+        <c:axId val="6942803"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="82956033"/>
+        <c:axId val="66932702"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6855,7 +6954,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="57581551"/>
+        <c:crossAx val="6942803"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6863,7 +6962,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="57581551"/>
+        <c:axId val="6942803"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6895,7 +6994,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="82956033"/>
+        <c:crossAx val="66932702"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7582,11 +7681,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="66318600"/>
-        <c:axId val="88783639"/>
+        <c:axId val="92653217"/>
+        <c:axId val="813901"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="66318600"/>
+        <c:axId val="92653217"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7618,7 +7717,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="88783639"/>
+        <c:crossAx val="813901"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7626,7 +7725,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="88783639"/>
+        <c:axId val="813901"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7658,7 +7757,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66318600"/>
+        <c:crossAx val="92653217"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7830,11 +7929,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="60487119"/>
-        <c:axId val="46071228"/>
+        <c:axId val="47307000"/>
+        <c:axId val="80984670"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="60487119"/>
+        <c:axId val="47307000"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7866,7 +7965,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="46071228"/>
+        <c:crossAx val="80984670"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7874,7 +7973,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="46071228"/>
+        <c:axId val="80984670"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7906,7 +8005,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="60487119"/>
+        <c:crossAx val="47307000"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8096,11 +8195,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="71686446"/>
-        <c:axId val="80485631"/>
+        <c:axId val="39916643"/>
+        <c:axId val="42632338"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="71686446"/>
+        <c:axId val="39916643"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8132,7 +8231,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80485631"/>
+        <c:crossAx val="42632338"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8140,7 +8239,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="80485631"/>
+        <c:axId val="42632338"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8172,7 +8271,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="71686446"/>
+        <c:crossAx val="39916643"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8356,11 +8455,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="9282771"/>
-        <c:axId val="37164128"/>
+        <c:axId val="81237978"/>
+        <c:axId val="91321989"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="9282771"/>
+        <c:axId val="81237978"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8392,7 +8491,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37164128"/>
+        <c:crossAx val="91321989"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8400,7 +8499,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="37164128"/>
+        <c:axId val="91321989"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8432,7 +8531,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="9282771"/>
+        <c:crossAx val="81237978"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8586,11 +8685,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="91602965"/>
-        <c:axId val="84366139"/>
+        <c:axId val="6538460"/>
+        <c:axId val="6466244"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="91602965"/>
+        <c:axId val="6538460"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8622,7 +8721,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="84366139"/>
+        <c:crossAx val="6466244"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8630,7 +8729,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="84366139"/>
+        <c:axId val="6466244"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8662,7 +8761,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="91602965"/>
+        <c:crossAx val="6538460"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8822,11 +8921,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="59003655"/>
-        <c:axId val="25491521"/>
+        <c:axId val="96345473"/>
+        <c:axId val="44745334"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="59003655"/>
+        <c:axId val="96345473"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8858,7 +8957,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="25491521"/>
+        <c:crossAx val="44745334"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8866,7 +8965,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="25491521"/>
+        <c:axId val="44745334"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8898,7 +8997,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="59003655"/>
+        <c:crossAx val="96345473"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11375,11 +11474,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="32516083"/>
-        <c:axId val="42938501"/>
+        <c:axId val="59724672"/>
+        <c:axId val="96350247"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="32516083"/>
+        <c:axId val="59724672"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11411,7 +11510,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="42938501"/>
+        <c:crossAx val="96350247"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11419,7 +11518,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="42938501"/>
+        <c:axId val="96350247"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11451,7 +11550,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="32516083"/>
+        <c:crossAx val="59724672"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11866,11 +11965,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="33366213"/>
-        <c:axId val="7906641"/>
+        <c:axId val="70580925"/>
+        <c:axId val="26268299"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="33366213"/>
+        <c:axId val="70580925"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11902,7 +12001,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="7906641"/>
+        <c:crossAx val="26268299"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11910,7 +12009,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="7906641"/>
+        <c:axId val="26268299"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11942,7 +12041,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="33366213"/>
+        <c:crossAx val="70580925"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12474,11 +12573,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="9374041"/>
-        <c:axId val="94208852"/>
+        <c:axId val="6515477"/>
+        <c:axId val="90905582"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="9374041"/>
+        <c:axId val="6515477"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12510,7 +12609,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94208852"/>
+        <c:crossAx val="90905582"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -12518,7 +12617,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="94208852"/>
+        <c:axId val="90905582"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12550,7 +12649,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="9374041"/>
+        <c:crossAx val="6515477"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12898,11 +12997,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="25309719"/>
-        <c:axId val="30541203"/>
+        <c:axId val="82684814"/>
+        <c:axId val="48528375"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="25309719"/>
+        <c:axId val="82684814"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12934,7 +13033,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="30541203"/>
+        <c:crossAx val="48528375"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -12942,7 +13041,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="30541203"/>
+        <c:axId val="48528375"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12974,7 +13073,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="25309719"/>
+        <c:crossAx val="82684814"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13206,11 +13305,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="18936560"/>
-        <c:axId val="49144451"/>
+        <c:axId val="89083684"/>
+        <c:axId val="67826004"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="18936560"/>
+        <c:axId val="89083684"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13242,7 +13341,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="49144451"/>
+        <c:crossAx val="67826004"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -13250,7 +13349,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="49144451"/>
+        <c:axId val="67826004"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13282,7 +13381,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="18936560"/>
+        <c:crossAx val="89083684"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14159,11 +14258,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="50772334"/>
-        <c:axId val="12516956"/>
+        <c:axId val="16220261"/>
+        <c:axId val="26435433"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="50772334"/>
+        <c:axId val="16220261"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14195,7 +14294,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="12516956"/>
+        <c:crossAx val="26435433"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -14203,7 +14302,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="12516956"/>
+        <c:axId val="26435433"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14235,7 +14334,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="50772334"/>
+        <c:crossAx val="16220261"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -17665,49 +17764,67 @@
       <c r="A4" s="94" t="s">
         <v>1249</v>
       </c>
-      <c r="B4" s="69"/>
-      <c r="C4" s="69"/>
-      <c r="D4" s="69"/>
+      <c r="B4" s="69" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C4" s="69" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D4" s="69" t="s">
+        <v>1288</v>
+      </c>
       <c r="E4" s="69"/>
       <c r="F4" s="69"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="94" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="B5" s="95" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="C5" s="95" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="D5" s="95" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="E5" s="95" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="F5" s="95" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="94" t="s">
-        <v>1289</v>
-      </c>
-      <c r="B6" s="69"/>
-      <c r="C6" s="69"/>
-      <c r="D6" s="69"/>
+        <v>1291</v>
+      </c>
+      <c r="B6" s="69" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C6" s="69" t="s">
+        <v>1292</v>
+      </c>
+      <c r="D6" s="69" t="s">
+        <v>1293</v>
+      </c>
       <c r="E6" s="69"/>
       <c r="F6" s="69"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="94" t="s">
-        <v>1290</v>
-      </c>
-      <c r="B7" s="69"/>
-      <c r="C7" s="69"/>
-      <c r="D7" s="69"/>
+        <v>1294</v>
+      </c>
+      <c r="B7" s="69" t="n">
+        <v>200</v>
+      </c>
+      <c r="C7" s="69" t="n">
+        <v>150</v>
+      </c>
+      <c r="D7" s="69" t="n">
+        <v>120</v>
+      </c>
       <c r="E7" s="69"/>
       <c r="F7" s="69"/>
     </row>
@@ -17715,99 +17832,159 @@
       <c r="A8" s="94" t="s">
         <v>1253</v>
       </c>
-      <c r="B8" s="69"/>
-      <c r="C8" s="69"/>
-      <c r="D8" s="69"/>
+      <c r="B8" s="69" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C8" s="69" t="s">
+        <v>1295</v>
+      </c>
+      <c r="D8" s="69" t="s">
+        <v>1296</v>
+      </c>
       <c r="E8" s="69"/>
       <c r="F8" s="69"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="94" t="s">
-        <v>1291</v>
-      </c>
-      <c r="B9" s="83"/>
-      <c r="C9" s="83"/>
-      <c r="D9" s="83"/>
+        <v>1297</v>
+      </c>
+      <c r="B9" s="83" t="n">
+        <v>8500</v>
+      </c>
+      <c r="C9" s="83" t="n">
+        <v>6000</v>
+      </c>
+      <c r="D9" s="83" t="n">
+        <v>7200</v>
+      </c>
       <c r="E9" s="83"/>
       <c r="F9" s="83"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="94" t="s">
-        <v>1292</v>
-      </c>
-      <c r="B10" s="83"/>
-      <c r="C10" s="83"/>
-      <c r="D10" s="83"/>
+        <v>1298</v>
+      </c>
+      <c r="B10" s="83" t="n">
+        <v>500</v>
+      </c>
+      <c r="C10" s="83" t="n">
+        <v>800</v>
+      </c>
+      <c r="D10" s="83" t="n">
+        <v>0</v>
+      </c>
       <c r="E10" s="83"/>
       <c r="F10" s="83"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="94" t="s">
-        <v>1293</v>
-      </c>
-      <c r="B11" s="83"/>
-      <c r="C11" s="83"/>
-      <c r="D11" s="83"/>
+        <v>1299</v>
+      </c>
+      <c r="B11" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="83" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D11" s="83" t="n">
+        <v>0</v>
+      </c>
       <c r="E11" s="83"/>
       <c r="F11" s="83"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="94" t="s">
-        <v>1294</v>
-      </c>
-      <c r="B12" s="83"/>
-      <c r="C12" s="83"/>
-      <c r="D12" s="83"/>
+        <v>1300</v>
+      </c>
+      <c r="B12" s="83" t="n">
+        <v>300</v>
+      </c>
+      <c r="C12" s="83" t="n">
+        <v>250</v>
+      </c>
+      <c r="D12" s="83" t="n">
+        <v>400</v>
+      </c>
       <c r="E12" s="83"/>
       <c r="F12" s="83"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="94" t="s">
-        <v>1295</v>
-      </c>
-      <c r="B13" s="83"/>
-      <c r="C13" s="83"/>
-      <c r="D13" s="83"/>
+        <v>1301</v>
+      </c>
+      <c r="B13" s="83" t="n">
+        <v>250</v>
+      </c>
+      <c r="C13" s="83" t="n">
+        <v>200</v>
+      </c>
+      <c r="D13" s="83" t="n">
+        <v>300</v>
+      </c>
       <c r="E13" s="83"/>
       <c r="F13" s="83"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="94" t="s">
-        <v>1296</v>
-      </c>
-      <c r="B14" s="83"/>
-      <c r="C14" s="83"/>
-      <c r="D14" s="83"/>
+        <v>1302</v>
+      </c>
+      <c r="B14" s="83" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C14" s="83" t="n">
+        <v>900</v>
+      </c>
+      <c r="D14" s="83" t="n">
+        <v>1100</v>
+      </c>
       <c r="E14" s="83"/>
       <c r="F14" s="83"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="94" t="s">
-        <v>1297</v>
-      </c>
-      <c r="B15" s="83"/>
-      <c r="C15" s="83"/>
-      <c r="D15" s="83"/>
+        <v>1303</v>
+      </c>
+      <c r="B15" s="83" t="n">
+        <v>6500</v>
+      </c>
+      <c r="C15" s="83" t="n">
+        <v>5200</v>
+      </c>
+      <c r="D15" s="83" t="n">
+        <v>7000</v>
+      </c>
       <c r="E15" s="83"/>
       <c r="F15" s="83"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="94" t="s">
-        <v>1298</v>
-      </c>
-      <c r="B16" s="83"/>
-      <c r="C16" s="83"/>
-      <c r="D16" s="83"/>
+        <v>1304</v>
+      </c>
+      <c r="B16" s="83" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C16" s="83" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D16" s="83" t="n">
+        <v>2200</v>
+      </c>
       <c r="E16" s="83"/>
       <c r="F16" s="83"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="94" t="s">
-        <v>1299</v>
-      </c>
-      <c r="B17" s="83"/>
-      <c r="C17" s="83"/>
-      <c r="D17" s="83"/>
+        <v>1305</v>
+      </c>
+      <c r="B17" s="83" t="n">
+        <v>150</v>
+      </c>
+      <c r="C17" s="83" t="n">
+        <v>200</v>
+      </c>
+      <c r="D17" s="83" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="83"/>
       <c r="F17" s="83"/>
     </row>
@@ -17817,15 +17994,15 @@
       </c>
       <c r="B18" s="96" t="n">
         <f aca="false">B9+B10+B11+B12+B13+B14+B15+B16+B17</f>
-        <v>0</v>
+        <v>19400</v>
       </c>
       <c r="C18" s="96" t="n">
         <f aca="false">C9+C10+C11+C12+C13+C14+C15+C16+C17</f>
-        <v>0</v>
+        <v>16250</v>
       </c>
       <c r="D18" s="96" t="n">
         <f aca="false">D9+D10+D11+D12+D13+D14+D15+D16+D17</f>
-        <v>0</v>
+        <v>18200</v>
       </c>
       <c r="E18" s="96" t="n">
         <f aca="false">E9+E10+E11+E12+E13+E14+E15+E16+E17</f>
@@ -17838,7 +18015,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="94" t="s">
-        <v>1300</v>
+        <v>1306</v>
       </c>
       <c r="B19" s="97" t="str">
         <f aca="false">IF(AND(B18&lt;&gt;0,B18=MIN(B18,C18,D18,E18,F18)),"Best Value","")</f>
@@ -17900,7 +18077,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="73" t="s">
-        <v>1301</v>
+        <v>1307</v>
       </c>
       <c r="B1" s="73"/>
       <c r="C1" s="73"/>
@@ -17913,12 +18090,12 @@
         <v>1000</v>
       </c>
       <c r="AE2" s="0" t="s">
-        <v>1302</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="98" t="s">
-        <v>1303</v>
+        <v>1309</v>
       </c>
       <c r="B3" s="98"/>
       <c r="C3" s="98"/>
@@ -17926,7 +18103,7 @@
       <c r="E3" s="98"/>
       <c r="F3" s="98"/>
       <c r="AD3" s="19" t="s">
-        <v>1304</v>
+        <v>1310</v>
       </c>
       <c r="AE3" s="89" t="n">
         <f aca="false">B32</f>
@@ -17935,7 +18112,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="55" t="s">
-        <v>1305</v>
+        <v>1311</v>
       </c>
       <c r="B4" s="55"/>
       <c r="C4" s="55"/>
@@ -17943,7 +18120,7 @@
       <c r="E4" s="55"/>
       <c r="F4" s="55"/>
       <c r="AD4" s="19" t="s">
-        <v>1306</v>
+        <v>1312</v>
       </c>
       <c r="AE4" s="89" t="n">
         <f aca="false">B64</f>
@@ -17958,13 +18135,13 @@
         <v>1153</v>
       </c>
       <c r="C5" s="56" t="s">
-        <v>1307</v>
+        <v>1313</v>
       </c>
       <c r="D5" s="56" t="s">
         <v>1207</v>
       </c>
       <c r="E5" s="56" t="s">
-        <v>1308</v>
+        <v>1314</v>
       </c>
       <c r="F5" s="56" t="s">
         <v>1231</v>
@@ -17975,7 +18152,7 @@
         <v>336</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>1309</v>
+        <v>1315</v>
       </c>
       <c r="C6" s="57"/>
       <c r="D6" s="86" t="n">
@@ -18042,7 +18219,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="55" t="s">
-        <v>1310</v>
+        <v>1316</v>
       </c>
       <c r="B11" s="55"/>
       <c r="C11" s="55"/>
@@ -18058,13 +18235,13 @@
         <v>1153</v>
       </c>
       <c r="C12" s="56" t="s">
-        <v>1307</v>
+        <v>1313</v>
       </c>
       <c r="D12" s="56" t="s">
         <v>1207</v>
       </c>
       <c r="E12" s="56" t="s">
-        <v>1308</v>
+        <v>1314</v>
       </c>
       <c r="F12" s="56" t="s">
         <v>1231</v>
@@ -18075,7 +18252,7 @@
         <v>336</v>
       </c>
       <c r="B13" s="57" t="s">
-        <v>1311</v>
+        <v>1317</v>
       </c>
       <c r="C13" s="57"/>
       <c r="D13" s="86" t="n">
@@ -18142,7 +18319,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="55" t="s">
-        <v>1312</v>
+        <v>1318</v>
       </c>
       <c r="B18" s="55"/>
       <c r="C18" s="55"/>
@@ -18158,13 +18335,13 @@
         <v>1153</v>
       </c>
       <c r="C19" s="56" t="s">
-        <v>1307</v>
+        <v>1313</v>
       </c>
       <c r="D19" s="56" t="s">
         <v>1207</v>
       </c>
       <c r="E19" s="56" t="s">
-        <v>1308</v>
+        <v>1314</v>
       </c>
       <c r="F19" s="56" t="s">
         <v>1231</v>
@@ -18175,7 +18352,7 @@
         <v>336</v>
       </c>
       <c r="B20" s="57" t="s">
-        <v>1313</v>
+        <v>1319</v>
       </c>
       <c r="C20" s="57"/>
       <c r="D20" s="86" t="n">
@@ -18242,7 +18419,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="55" t="s">
-        <v>1314</v>
+        <v>1320</v>
       </c>
       <c r="B25" s="55"/>
       <c r="C25" s="55"/>
@@ -18258,13 +18435,13 @@
         <v>1153</v>
       </c>
       <c r="C26" s="56" t="s">
-        <v>1307</v>
+        <v>1313</v>
       </c>
       <c r="D26" s="56" t="s">
         <v>1207</v>
       </c>
       <c r="E26" s="56" t="s">
-        <v>1308</v>
+        <v>1314</v>
       </c>
       <c r="F26" s="56" t="s">
         <v>1231</v>
@@ -18275,7 +18452,7 @@
         <v>336</v>
       </c>
       <c r="B27" s="57" t="s">
-        <v>1315</v>
+        <v>1321</v>
       </c>
       <c r="C27" s="57"/>
       <c r="D27" s="86" t="n">
@@ -18342,7 +18519,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="99" t="s">
-        <v>1316</v>
+        <v>1322</v>
       </c>
       <c r="B32" s="100" t="n">
         <f aca="false">SUM(F6:F9)+SUM(F13:F16)+SUM(F20:F23)+SUM(F27:F30)</f>
@@ -18361,7 +18538,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="55" t="s">
-        <v>1305</v>
+        <v>1311</v>
       </c>
       <c r="B36" s="55"/>
       <c r="C36" s="55"/>
@@ -18377,13 +18554,13 @@
         <v>1153</v>
       </c>
       <c r="C37" s="56" t="s">
-        <v>1307</v>
+        <v>1313</v>
       </c>
       <c r="D37" s="56" t="s">
         <v>1207</v>
       </c>
       <c r="E37" s="56" t="s">
-        <v>1308</v>
+        <v>1314</v>
       </c>
       <c r="F37" s="56" t="s">
         <v>1231</v>
@@ -18394,7 +18571,7 @@
         <v>336</v>
       </c>
       <c r="B38" s="57" t="s">
-        <v>1317</v>
+        <v>1323</v>
       </c>
       <c r="C38" s="57"/>
       <c r="D38" s="86" t="n">
@@ -18461,7 +18638,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="55" t="s">
-        <v>1310</v>
+        <v>1316</v>
       </c>
       <c r="B43" s="55"/>
       <c r="C43" s="55"/>
@@ -18477,13 +18654,13 @@
         <v>1153</v>
       </c>
       <c r="C44" s="56" t="s">
-        <v>1307</v>
+        <v>1313</v>
       </c>
       <c r="D44" s="56" t="s">
         <v>1207</v>
       </c>
       <c r="E44" s="56" t="s">
-        <v>1308</v>
+        <v>1314</v>
       </c>
       <c r="F44" s="56" t="s">
         <v>1231</v>
@@ -18494,7 +18671,7 @@
         <v>336</v>
       </c>
       <c r="B45" s="57" t="s">
-        <v>1318</v>
+        <v>1324</v>
       </c>
       <c r="C45" s="57"/>
       <c r="D45" s="86" t="n">
@@ -18561,7 +18738,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="55" t="s">
-        <v>1312</v>
+        <v>1318</v>
       </c>
       <c r="B50" s="55"/>
       <c r="C50" s="55"/>
@@ -18577,13 +18754,13 @@
         <v>1153</v>
       </c>
       <c r="C51" s="56" t="s">
-        <v>1307</v>
+        <v>1313</v>
       </c>
       <c r="D51" s="56" t="s">
         <v>1207</v>
       </c>
       <c r="E51" s="56" t="s">
-        <v>1308</v>
+        <v>1314</v>
       </c>
       <c r="F51" s="56" t="s">
         <v>1231</v>
@@ -18594,7 +18771,7 @@
         <v>336</v>
       </c>
       <c r="B52" s="57" t="s">
-        <v>1319</v>
+        <v>1325</v>
       </c>
       <c r="C52" s="57"/>
       <c r="D52" s="86" t="n">
@@ -18661,7 +18838,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="55" t="s">
-        <v>1314</v>
+        <v>1320</v>
       </c>
       <c r="B57" s="55"/>
       <c r="C57" s="55"/>
@@ -18677,13 +18854,13 @@
         <v>1153</v>
       </c>
       <c r="C58" s="56" t="s">
-        <v>1307</v>
+        <v>1313</v>
       </c>
       <c r="D58" s="56" t="s">
         <v>1207</v>
       </c>
       <c r="E58" s="56" t="s">
-        <v>1308</v>
+        <v>1314</v>
       </c>
       <c r="F58" s="56" t="s">
         <v>1231</v>
@@ -18694,7 +18871,7 @@
         <v>336</v>
       </c>
       <c r="B59" s="57" t="s">
-        <v>1320</v>
+        <v>1326</v>
       </c>
       <c r="C59" s="57"/>
       <c r="D59" s="86" t="n">
@@ -18761,7 +18938,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="99" t="s">
-        <v>1321</v>
+        <v>1327</v>
       </c>
       <c r="B64" s="100" t="n">
         <f aca="false">SUM(F38:F41)+SUM(F45:F48)+SUM(F52:F55)+SUM(F59:F62)</f>
@@ -18842,31 +19019,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="75" t="s">
-        <v>1322</v>
+        <v>1328</v>
       </c>
       <c r="B1" s="75"/>
       <c r="C1" s="75"/>
     </row>
     <row r="3" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="101" t="s">
-        <v>1323</v>
+        <v>1329</v>
       </c>
       <c r="B3" s="101"/>
       <c r="C3" s="101"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="55" t="s">
-        <v>1324</v>
+        <v>1330</v>
       </c>
       <c r="B4" s="55"/>
       <c r="C4" s="55"/>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="56" t="s">
-        <v>1325</v>
+        <v>1331</v>
       </c>
       <c r="B5" s="56" t="s">
-        <v>1326</v>
+        <v>1332</v>
       </c>
       <c r="C5" s="56" t="s">
         <v>1155</v>
@@ -18877,7 +19054,7 @@
         <v>336</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>1327</v>
+        <v>1333</v>
       </c>
       <c r="C6" s="57"/>
     </row>
@@ -18886,7 +19063,7 @@
         <v>336</v>
       </c>
       <c r="B7" s="59" t="s">
-        <v>1328</v>
+        <v>1334</v>
       </c>
       <c r="C7" s="59"/>
     </row>
@@ -18895,7 +19072,7 @@
         <v>336</v>
       </c>
       <c r="B8" s="57" t="s">
-        <v>1329</v>
+        <v>1335</v>
       </c>
       <c r="C8" s="57"/>
     </row>
@@ -18904,7 +19081,7 @@
         <v>336</v>
       </c>
       <c r="B9" s="59" t="s">
-        <v>1330</v>
+        <v>1336</v>
       </c>
       <c r="C9" s="59"/>
     </row>
@@ -18913,7 +19090,7 @@
         <v>336</v>
       </c>
       <c r="B10" s="57" t="s">
-        <v>1331</v>
+        <v>1337</v>
       </c>
       <c r="C10" s="57"/>
     </row>
@@ -18922,7 +19099,7 @@
         <v>336</v>
       </c>
       <c r="B11" s="59" t="s">
-        <v>1332</v>
+        <v>1338</v>
       </c>
       <c r="C11" s="59"/>
     </row>
@@ -18931,7 +19108,7 @@
         <v>336</v>
       </c>
       <c r="B12" s="57" t="s">
-        <v>1333</v>
+        <v>1339</v>
       </c>
       <c r="C12" s="57"/>
     </row>
@@ -18940,7 +19117,7 @@
         <v>336</v>
       </c>
       <c r="B13" s="59" t="s">
-        <v>1334</v>
+        <v>1340</v>
       </c>
       <c r="C13" s="59"/>
     </row>
@@ -18953,10 +19130,10 @@
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="56" t="s">
-        <v>1325</v>
+        <v>1331</v>
       </c>
       <c r="B16" s="56" t="s">
-        <v>1326</v>
+        <v>1332</v>
       </c>
       <c r="C16" s="56" t="s">
         <v>1155</v>
@@ -18967,7 +19144,7 @@
         <v>336</v>
       </c>
       <c r="B17" s="57" t="s">
-        <v>1335</v>
+        <v>1341</v>
       </c>
       <c r="C17" s="57"/>
     </row>
@@ -18976,7 +19153,7 @@
         <v>336</v>
       </c>
       <c r="B18" s="59" t="s">
-        <v>1336</v>
+        <v>1342</v>
       </c>
       <c r="C18" s="59"/>
     </row>
@@ -18994,7 +19171,7 @@
         <v>336</v>
       </c>
       <c r="B20" s="59" t="s">
-        <v>1337</v>
+        <v>1343</v>
       </c>
       <c r="C20" s="59"/>
     </row>
@@ -19003,7 +19180,7 @@
         <v>336</v>
       </c>
       <c r="B21" s="57" t="s">
-        <v>1338</v>
+        <v>1344</v>
       </c>
       <c r="C21" s="57"/>
     </row>
@@ -19012,7 +19189,7 @@
         <v>336</v>
       </c>
       <c r="B22" s="59" t="s">
-        <v>1339</v>
+        <v>1345</v>
       </c>
       <c r="C22" s="59"/>
     </row>
@@ -19021,7 +19198,7 @@
         <v>336</v>
       </c>
       <c r="B23" s="57" t="s">
-        <v>1340</v>
+        <v>1346</v>
       </c>
       <c r="C23" s="57"/>
     </row>
@@ -19036,17 +19213,17 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="55" t="s">
-        <v>1341</v>
+        <v>1347</v>
       </c>
       <c r="B26" s="55"/>
       <c r="C26" s="55"/>
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="56" t="s">
-        <v>1325</v>
+        <v>1331</v>
       </c>
       <c r="B27" s="56" t="s">
-        <v>1326</v>
+        <v>1332</v>
       </c>
       <c r="C27" s="56" t="s">
         <v>1155</v>
@@ -19057,7 +19234,7 @@
         <v>336</v>
       </c>
       <c r="B28" s="57" t="s">
-        <v>1342</v>
+        <v>1348</v>
       </c>
       <c r="C28" s="57"/>
     </row>
@@ -19066,7 +19243,7 @@
         <v>336</v>
       </c>
       <c r="B29" s="59" t="s">
-        <v>1343</v>
+        <v>1349</v>
       </c>
       <c r="C29" s="59"/>
     </row>
@@ -19075,7 +19252,7 @@
         <v>336</v>
       </c>
       <c r="B30" s="57" t="s">
-        <v>1344</v>
+        <v>1350</v>
       </c>
       <c r="C30" s="57"/>
     </row>
@@ -19084,7 +19261,7 @@
         <v>336</v>
       </c>
       <c r="B31" s="59" t="s">
-        <v>1345</v>
+        <v>1351</v>
       </c>
       <c r="C31" s="59"/>
     </row>
@@ -19093,7 +19270,7 @@
         <v>336</v>
       </c>
       <c r="B32" s="57" t="s">
-        <v>1346</v>
+        <v>1352</v>
       </c>
       <c r="C32" s="57"/>
     </row>
@@ -19102,7 +19279,7 @@
         <v>336</v>
       </c>
       <c r="B33" s="59" t="s">
-        <v>1347</v>
+        <v>1353</v>
       </c>
       <c r="C33" s="59"/>
     </row>
@@ -19115,10 +19292,10 @@
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="56" t="s">
-        <v>1325</v>
+        <v>1331</v>
       </c>
       <c r="B36" s="56" t="s">
-        <v>1326</v>
+        <v>1332</v>
       </c>
       <c r="C36" s="56" t="s">
         <v>1155</v>
@@ -19129,7 +19306,7 @@
         <v>336</v>
       </c>
       <c r="B37" s="57" t="s">
-        <v>1348</v>
+        <v>1354</v>
       </c>
       <c r="C37" s="57"/>
     </row>
@@ -19138,7 +19315,7 @@
         <v>336</v>
       </c>
       <c r="B38" s="59" t="s">
-        <v>1349</v>
+        <v>1355</v>
       </c>
       <c r="C38" s="59"/>
     </row>
@@ -19147,7 +19324,7 @@
         <v>336</v>
       </c>
       <c r="B39" s="57" t="s">
-        <v>1350</v>
+        <v>1356</v>
       </c>
       <c r="C39" s="57"/>
     </row>
@@ -19156,7 +19333,7 @@
         <v>336</v>
       </c>
       <c r="B40" s="59" t="s">
-        <v>1351</v>
+        <v>1357</v>
       </c>
       <c r="C40" s="59"/>
     </row>
@@ -19165,7 +19342,7 @@
         <v>336</v>
       </c>
       <c r="B41" s="57" t="s">
-        <v>1352</v>
+        <v>1358</v>
       </c>
       <c r="C41" s="57"/>
     </row>
@@ -19174,7 +19351,7 @@
         <v>336</v>
       </c>
       <c r="B42" s="59" t="s">
-        <v>1353</v>
+        <v>1359</v>
       </c>
       <c r="C42" s="59"/>
     </row>
@@ -19183,7 +19360,7 @@
         <v>336</v>
       </c>
       <c r="B43" s="57" t="s">
-        <v>1354</v>
+        <v>1360</v>
       </c>
       <c r="C43" s="57"/>
     </row>
@@ -19192,7 +19369,7 @@
         <v>336</v>
       </c>
       <c r="B44" s="59" t="s">
-        <v>1355</v>
+        <v>1361</v>
       </c>
       <c r="C44" s="59"/>
     </row>
@@ -19201,7 +19378,7 @@
         <v>336</v>
       </c>
       <c r="B45" s="57" t="s">
-        <v>1356</v>
+        <v>1362</v>
       </c>
       <c r="C45" s="57"/>
     </row>
@@ -19210,23 +19387,23 @@
         <v>336</v>
       </c>
       <c r="B46" s="59" t="s">
-        <v>1357</v>
+        <v>1363</v>
       </c>
       <c r="C46" s="59"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="55" t="s">
-        <v>1358</v>
+        <v>1364</v>
       </c>
       <c r="B48" s="55"/>
       <c r="C48" s="55"/>
     </row>
     <row r="49" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="56" t="s">
-        <v>1325</v>
+        <v>1331</v>
       </c>
       <c r="B49" s="56" t="s">
-        <v>1326</v>
+        <v>1332</v>
       </c>
       <c r="C49" s="56" t="s">
         <v>1155</v>
@@ -19246,7 +19423,7 @@
         <v>336</v>
       </c>
       <c r="B51" s="59" t="s">
-        <v>1359</v>
+        <v>1365</v>
       </c>
       <c r="C51" s="59"/>
     </row>
@@ -19264,7 +19441,7 @@
         <v>336</v>
       </c>
       <c r="B53" s="59" t="s">
-        <v>1360</v>
+        <v>1366</v>
       </c>
       <c r="C53" s="59"/>
     </row>
@@ -19273,7 +19450,7 @@
         <v>336</v>
       </c>
       <c r="B54" s="57" t="s">
-        <v>1361</v>
+        <v>1367</v>
       </c>
       <c r="C54" s="57"/>
     </row>
@@ -19300,30 +19477,30 @@
         <v>336</v>
       </c>
       <c r="B57" s="59" t="s">
-        <v>1362</v>
+        <v>1368</v>
       </c>
       <c r="C57" s="59"/>
     </row>
     <row r="59" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="101" t="s">
-        <v>1363</v>
+        <v>1369</v>
       </c>
       <c r="B59" s="101"/>
       <c r="C59" s="101"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="55" t="s">
-        <v>1324</v>
+        <v>1330</v>
       </c>
       <c r="B60" s="55"/>
       <c r="C60" s="55"/>
     </row>
     <row r="61" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="56" t="s">
-        <v>1325</v>
+        <v>1331</v>
       </c>
       <c r="B61" s="56" t="s">
-        <v>1326</v>
+        <v>1332</v>
       </c>
       <c r="C61" s="56" t="s">
         <v>1155</v>
@@ -19334,7 +19511,7 @@
         <v>336</v>
       </c>
       <c r="B62" s="57" t="s">
-        <v>1327</v>
+        <v>1333</v>
       </c>
       <c r="C62" s="57"/>
     </row>
@@ -19343,7 +19520,7 @@
         <v>336</v>
       </c>
       <c r="B63" s="59" t="s">
-        <v>1328</v>
+        <v>1334</v>
       </c>
       <c r="C63" s="59"/>
     </row>
@@ -19352,7 +19529,7 @@
         <v>336</v>
       </c>
       <c r="B64" s="57" t="s">
-        <v>1329</v>
+        <v>1335</v>
       </c>
       <c r="C64" s="57"/>
     </row>
@@ -19361,7 +19538,7 @@
         <v>336</v>
       </c>
       <c r="B65" s="59" t="s">
-        <v>1330</v>
+        <v>1336</v>
       </c>
       <c r="C65" s="59"/>
     </row>
@@ -19370,7 +19547,7 @@
         <v>336</v>
       </c>
       <c r="B66" s="57" t="s">
-        <v>1331</v>
+        <v>1337</v>
       </c>
       <c r="C66" s="57"/>
     </row>
@@ -19379,7 +19556,7 @@
         <v>336</v>
       </c>
       <c r="B67" s="59" t="s">
-        <v>1332</v>
+        <v>1338</v>
       </c>
       <c r="C67" s="59"/>
     </row>
@@ -19388,7 +19565,7 @@
         <v>336</v>
       </c>
       <c r="B68" s="57" t="s">
-        <v>1333</v>
+        <v>1339</v>
       </c>
       <c r="C68" s="57"/>
     </row>
@@ -19397,7 +19574,7 @@
         <v>336</v>
       </c>
       <c r="B69" s="59" t="s">
-        <v>1334</v>
+        <v>1340</v>
       </c>
       <c r="C69" s="59"/>
     </row>
@@ -19410,10 +19587,10 @@
     </row>
     <row r="72" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="56" t="s">
-        <v>1325</v>
+        <v>1331</v>
       </c>
       <c r="B72" s="56" t="s">
-        <v>1326</v>
+        <v>1332</v>
       </c>
       <c r="C72" s="56" t="s">
         <v>1155</v>
@@ -19424,7 +19601,7 @@
         <v>336</v>
       </c>
       <c r="B73" s="57" t="s">
-        <v>1335</v>
+        <v>1341</v>
       </c>
       <c r="C73" s="57"/>
     </row>
@@ -19433,7 +19610,7 @@
         <v>336</v>
       </c>
       <c r="B74" s="59" t="s">
-        <v>1336</v>
+        <v>1342</v>
       </c>
       <c r="C74" s="59"/>
     </row>
@@ -19451,7 +19628,7 @@
         <v>336</v>
       </c>
       <c r="B76" s="59" t="s">
-        <v>1337</v>
+        <v>1343</v>
       </c>
       <c r="C76" s="59"/>
     </row>
@@ -19460,7 +19637,7 @@
         <v>336</v>
       </c>
       <c r="B77" s="57" t="s">
-        <v>1338</v>
+        <v>1344</v>
       </c>
       <c r="C77" s="57"/>
     </row>
@@ -19469,7 +19646,7 @@
         <v>336</v>
       </c>
       <c r="B78" s="59" t="s">
-        <v>1339</v>
+        <v>1345</v>
       </c>
       <c r="C78" s="59"/>
     </row>
@@ -19478,7 +19655,7 @@
         <v>336</v>
       </c>
       <c r="B79" s="57" t="s">
-        <v>1340</v>
+        <v>1346</v>
       </c>
       <c r="C79" s="57"/>
     </row>
@@ -19493,17 +19670,17 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="55" t="s">
-        <v>1341</v>
+        <v>1347</v>
       </c>
       <c r="B82" s="55"/>
       <c r="C82" s="55"/>
     </row>
     <row r="83" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="56" t="s">
-        <v>1325</v>
+        <v>1331</v>
       </c>
       <c r="B83" s="56" t="s">
-        <v>1326</v>
+        <v>1332</v>
       </c>
       <c r="C83" s="56" t="s">
         <v>1155</v>
@@ -19514,7 +19691,7 @@
         <v>336</v>
       </c>
       <c r="B84" s="57" t="s">
-        <v>1342</v>
+        <v>1348</v>
       </c>
       <c r="C84" s="57"/>
     </row>
@@ -19523,7 +19700,7 @@
         <v>336</v>
       </c>
       <c r="B85" s="59" t="s">
-        <v>1343</v>
+        <v>1349</v>
       </c>
       <c r="C85" s="59"/>
     </row>
@@ -19532,7 +19709,7 @@
         <v>336</v>
       </c>
       <c r="B86" s="57" t="s">
-        <v>1344</v>
+        <v>1350</v>
       </c>
       <c r="C86" s="57"/>
     </row>
@@ -19541,7 +19718,7 @@
         <v>336</v>
       </c>
       <c r="B87" s="59" t="s">
-        <v>1345</v>
+        <v>1351</v>
       </c>
       <c r="C87" s="59"/>
     </row>
@@ -19550,7 +19727,7 @@
         <v>336</v>
       </c>
       <c r="B88" s="57" t="s">
-        <v>1346</v>
+        <v>1352</v>
       </c>
       <c r="C88" s="57"/>
     </row>
@@ -19559,7 +19736,7 @@
         <v>336</v>
       </c>
       <c r="B89" s="59" t="s">
-        <v>1347</v>
+        <v>1353</v>
       </c>
       <c r="C89" s="59"/>
     </row>
@@ -19572,10 +19749,10 @@
     </row>
     <row r="92" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="56" t="s">
-        <v>1325</v>
+        <v>1331</v>
       </c>
       <c r="B92" s="56" t="s">
-        <v>1326</v>
+        <v>1332</v>
       </c>
       <c r="C92" s="56" t="s">
         <v>1155</v>
@@ -19586,7 +19763,7 @@
         <v>336</v>
       </c>
       <c r="B93" s="57" t="s">
-        <v>1348</v>
+        <v>1354</v>
       </c>
       <c r="C93" s="57"/>
     </row>
@@ -19595,7 +19772,7 @@
         <v>336</v>
       </c>
       <c r="B94" s="59" t="s">
-        <v>1349</v>
+        <v>1355</v>
       </c>
       <c r="C94" s="59"/>
     </row>
@@ -19604,7 +19781,7 @@
         <v>336</v>
       </c>
       <c r="B95" s="57" t="s">
-        <v>1350</v>
+        <v>1356</v>
       </c>
       <c r="C95" s="57"/>
     </row>
@@ -19613,7 +19790,7 @@
         <v>336</v>
       </c>
       <c r="B96" s="59" t="s">
-        <v>1351</v>
+        <v>1357</v>
       </c>
       <c r="C96" s="59"/>
     </row>
@@ -19622,7 +19799,7 @@
         <v>336</v>
       </c>
       <c r="B97" s="57" t="s">
-        <v>1352</v>
+        <v>1358</v>
       </c>
       <c r="C97" s="57"/>
     </row>
@@ -19631,7 +19808,7 @@
         <v>336</v>
       </c>
       <c r="B98" s="59" t="s">
-        <v>1353</v>
+        <v>1359</v>
       </c>
       <c r="C98" s="59"/>
     </row>
@@ -19640,7 +19817,7 @@
         <v>336</v>
       </c>
       <c r="B99" s="57" t="s">
-        <v>1354</v>
+        <v>1360</v>
       </c>
       <c r="C99" s="57"/>
     </row>
@@ -19649,7 +19826,7 @@
         <v>336</v>
       </c>
       <c r="B100" s="59" t="s">
-        <v>1355</v>
+        <v>1361</v>
       </c>
       <c r="C100" s="59"/>
     </row>
@@ -19658,7 +19835,7 @@
         <v>336</v>
       </c>
       <c r="B101" s="57" t="s">
-        <v>1356</v>
+        <v>1362</v>
       </c>
       <c r="C101" s="57"/>
     </row>
@@ -19667,23 +19844,23 @@
         <v>336</v>
       </c>
       <c r="B102" s="59" t="s">
-        <v>1357</v>
+        <v>1363</v>
       </c>
       <c r="C102" s="59"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="55" t="s">
-        <v>1358</v>
+        <v>1364</v>
       </c>
       <c r="B104" s="55"/>
       <c r="C104" s="55"/>
     </row>
     <row r="105" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="56" t="s">
-        <v>1325</v>
+        <v>1331</v>
       </c>
       <c r="B105" s="56" t="s">
-        <v>1326</v>
+        <v>1332</v>
       </c>
       <c r="C105" s="56" t="s">
         <v>1155</v>
@@ -19703,7 +19880,7 @@
         <v>336</v>
       </c>
       <c r="B107" s="59" t="s">
-        <v>1359</v>
+        <v>1365</v>
       </c>
       <c r="C107" s="59"/>
     </row>
@@ -19721,7 +19898,7 @@
         <v>336</v>
       </c>
       <c r="B109" s="59" t="s">
-        <v>1360</v>
+        <v>1366</v>
       </c>
       <c r="C109" s="59"/>
     </row>
@@ -19730,7 +19907,7 @@
         <v>336</v>
       </c>
       <c r="B110" s="57" t="s">
-        <v>1361</v>
+        <v>1367</v>
       </c>
       <c r="C110" s="57"/>
     </row>
@@ -19757,7 +19934,7 @@
         <v>336</v>
       </c>
       <c r="B113" s="59" t="s">
-        <v>1362</v>
+        <v>1368</v>
       </c>
       <c r="C113" s="59"/>
     </row>
@@ -19901,7 +20078,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="102" t="s">
-        <v>1364</v>
+        <v>1370</v>
       </c>
       <c r="B1" s="102"/>
       <c r="C1" s="102"/>
@@ -19917,7 +20094,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD2" s="99" t="s">
-        <v>1365</v>
+        <v>1371</v>
       </c>
       <c r="AE2" s="99" t="s">
         <v>130</v>
@@ -19925,27 +20102,27 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="21" t="s">
-        <v>1366</v>
+        <v>1372</v>
       </c>
       <c r="B3" s="21"/>
       <c r="C3" s="21" t="s">
-        <v>1367</v>
+        <v>1373</v>
       </c>
       <c r="D3" s="21"/>
       <c r="E3" s="21" t="s">
-        <v>1368</v>
+        <v>1374</v>
       </c>
       <c r="F3" s="21"/>
       <c r="G3" s="21" t="s">
-        <v>1369</v>
+        <v>1375</v>
       </c>
       <c r="H3" s="21"/>
       <c r="I3" s="21" t="s">
-        <v>1370</v>
+        <v>1376</v>
       </c>
       <c r="J3" s="21"/>
       <c r="K3" s="21" t="s">
-        <v>1371</v>
+        <v>1377</v>
       </c>
       <c r="L3" s="21"/>
       <c r="AD3" s="19" t="s">
@@ -20009,25 +20186,25 @@
         <v>1249</v>
       </c>
       <c r="B6" s="79" t="s">
-        <v>1372</v>
+        <v>1378</v>
       </c>
       <c r="C6" s="79" t="s">
-        <v>1373</v>
+        <v>1379</v>
       </c>
       <c r="D6" s="79" t="s">
-        <v>1374</v>
+        <v>1380</v>
       </c>
       <c r="E6" s="79" t="s">
-        <v>1375</v>
+        <v>1381</v>
       </c>
       <c r="F6" s="79" t="s">
-        <v>1376</v>
+        <v>1382</v>
       </c>
       <c r="G6" s="79" t="s">
-        <v>1377</v>
+        <v>1383</v>
       </c>
       <c r="H6" s="79" t="s">
-        <v>1304</v>
+        <v>1310</v>
       </c>
       <c r="I6" s="79" t="s">
         <v>1250</v>
@@ -20036,12 +20213,12 @@
         <v>1251</v>
       </c>
       <c r="K6" s="79" t="s">
-        <v>1378</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="57" t="s">
-        <v>1379</v>
+        <v>1385</v>
       </c>
       <c r="B7" s="57" t="s">
         <v>58</v>
@@ -20059,7 +20236,7 @@
         <v>1255</v>
       </c>
       <c r="G7" s="57" t="s">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="H7" s="67" t="s">
         <v>336</v>
@@ -20068,7 +20245,7 @@
       <c r="J7" s="57"/>
       <c r="K7" s="57"/>
       <c r="AD7" s="99" t="s">
-        <v>1381</v>
+        <v>1387</v>
       </c>
       <c r="AE7" s="99" t="s">
         <v>130</v>
@@ -20076,7 +20253,7 @@
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>1382</v>
+        <v>1388</v>
       </c>
       <c r="B8" s="59" t="s">
         <v>66</v>
@@ -20094,7 +20271,7 @@
         <v>1269</v>
       </c>
       <c r="G8" s="59" t="s">
-        <v>1383</v>
+        <v>1389</v>
       </c>
       <c r="H8" s="65" t="s">
         <v>336</v>
@@ -20103,7 +20280,7 @@
       <c r="J8" s="59"/>
       <c r="K8" s="59"/>
       <c r="AD8" s="19" t="s">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="AE8" s="19" t="n">
         <f aca="false">COUNTIFS($G$7:$G$206,AD8)</f>
@@ -20112,7 +20289,7 @@
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="57" t="s">
-        <v>1384</v>
+        <v>1390</v>
       </c>
       <c r="B9" s="57" t="s">
         <v>67</v>
@@ -20127,10 +20304,10 @@
         <v>100</v>
       </c>
       <c r="F9" s="57" t="s">
-        <v>1385</v>
+        <v>1391</v>
       </c>
       <c r="G9" s="57" t="s">
-        <v>1386</v>
+        <v>1392</v>
       </c>
       <c r="H9" s="67" t="s">
         <v>336</v>
@@ -20139,7 +20316,7 @@
       <c r="J9" s="57"/>
       <c r="K9" s="57"/>
       <c r="AD9" s="19" t="s">
-        <v>1383</v>
+        <v>1389</v>
       </c>
       <c r="AE9" s="19" t="n">
         <f aca="false">COUNTIFS($G$7:$G$206,AD9)</f>
@@ -20148,7 +20325,7 @@
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="59" t="s">
-        <v>1387</v>
+        <v>1393</v>
       </c>
       <c r="B10" s="59" t="s">
         <v>58</v>
@@ -20166,7 +20343,7 @@
         <v>1255</v>
       </c>
       <c r="G10" s="59" t="s">
-        <v>1388</v>
+        <v>1394</v>
       </c>
       <c r="H10" s="65" t="s">
         <v>336</v>
@@ -20175,7 +20352,7 @@
       <c r="J10" s="59"/>
       <c r="K10" s="59"/>
       <c r="AD10" s="19" t="s">
-        <v>1386</v>
+        <v>1392</v>
       </c>
       <c r="AE10" s="19" t="n">
         <f aca="false">COUNTIFS($G$7:$G$206,AD10)</f>
@@ -20184,7 +20361,7 @@
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="57" t="s">
-        <v>1389</v>
+        <v>1395</v>
       </c>
       <c r="B11" s="57" t="s">
         <v>66</v>
@@ -20202,7 +20379,7 @@
         <v>1269</v>
       </c>
       <c r="G11" s="57" t="s">
-        <v>1390</v>
+        <v>1396</v>
       </c>
       <c r="H11" s="67" t="s">
         <v>336</v>
@@ -20211,7 +20388,7 @@
       <c r="J11" s="57"/>
       <c r="K11" s="57"/>
       <c r="AD11" s="19" t="s">
-        <v>1388</v>
+        <v>1394</v>
       </c>
       <c r="AE11" s="19" t="n">
         <f aca="false">COUNTIFS($G$7:$G$206,AD11)</f>
@@ -20220,7 +20397,7 @@
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="59" t="s">
-        <v>1391</v>
+        <v>1397</v>
       </c>
       <c r="B12" s="59" t="s">
         <v>67</v>
@@ -20235,10 +20412,10 @@
         <v>100</v>
       </c>
       <c r="F12" s="59" t="s">
-        <v>1385</v>
+        <v>1391</v>
       </c>
       <c r="G12" s="59" t="s">
-        <v>1392</v>
+        <v>1398</v>
       </c>
       <c r="H12" s="65" t="s">
         <v>336</v>
@@ -20247,7 +20424,7 @@
       <c r="J12" s="59"/>
       <c r="K12" s="59"/>
       <c r="AD12" s="19" t="s">
-        <v>1390</v>
+        <v>1396</v>
       </c>
       <c r="AE12" s="19" t="n">
         <f aca="false">COUNTIFS($G$7:$G$206,AD12)</f>
@@ -20275,7 +20452,7 @@
       <c r="J13" s="57"/>
       <c r="K13" s="57"/>
       <c r="AD13" s="19" t="s">
-        <v>1392</v>
+        <v>1398</v>
       </c>
       <c r="AE13" s="19" t="n">
         <f aca="false">COUNTIFS($G$7:$G$206,AD13)</f>
@@ -20303,7 +20480,7 @@
       <c r="J14" s="59"/>
       <c r="K14" s="59"/>
       <c r="AD14" s="19" t="s">
-        <v>1393</v>
+        <v>1399</v>
       </c>
       <c r="AE14" s="19" t="n">
         <f aca="false">COUNTIFS($G$7:$G$206,AD14)</f>
@@ -24427,7 +24604,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="75" t="s">
-        <v>1394</v>
+        <v>1400</v>
       </c>
       <c r="B1" s="75"/>
       <c r="C1" s="75"/>
@@ -24441,7 +24618,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="22" t="s">
-        <v>1395</v>
+        <v>1401</v>
       </c>
       <c r="B3" s="22"/>
       <c r="C3" s="22" t="s">
@@ -24449,19 +24626,19 @@
       </c>
       <c r="D3" s="22"/>
       <c r="E3" s="22" t="s">
-        <v>1396</v>
+        <v>1402</v>
       </c>
       <c r="F3" s="22"/>
       <c r="G3" s="22" t="s">
-        <v>1397</v>
+        <v>1403</v>
       </c>
       <c r="H3" s="22"/>
       <c r="I3" s="22" t="s">
-        <v>1398</v>
+        <v>1404</v>
       </c>
       <c r="J3" s="22"/>
       <c r="K3" s="22" t="s">
-        <v>1399</v>
+        <v>1405</v>
       </c>
       <c r="L3" s="22"/>
     </row>
@@ -24499,7 +24676,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="62" t="s">
-        <v>1400</v>
+        <v>1406</v>
       </c>
       <c r="B6" s="62"/>
       <c r="C6" s="62"/>
@@ -24509,7 +24686,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="55" t="s">
-        <v>1401</v>
+        <v>1407</v>
       </c>
       <c r="B8" s="55"/>
       <c r="C8" s="55"/>
@@ -24520,13 +24697,13 @@
         <v>1249</v>
       </c>
       <c r="B9" s="56" t="s">
-        <v>1372</v>
+        <v>1378</v>
       </c>
       <c r="C9" s="56" t="s">
-        <v>1376</v>
+        <v>1382</v>
       </c>
       <c r="D9" s="56" t="s">
-        <v>1402</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24831,18 +25008,18 @@
     </row>
     <row r="31" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="106" t="s">
-        <v>1403</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="107" t="s">
-        <v>1404</v>
+        <v>1410</v>
       </c>
       <c r="B32" s="107"/>
       <c r="C32" s="107"/>
       <c r="D32" s="107"/>
       <c r="G32" s="107" t="s">
-        <v>1405</v>
+        <v>1411</v>
       </c>
       <c r="H32" s="107"/>
       <c r="I32" s="107"/>
@@ -24850,26 +25027,26 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="108" t="s">
-        <v>1290</v>
+        <v>1294</v>
       </c>
       <c r="B33" s="108" t="n">
         <v>8</v>
       </c>
       <c r="C33" s="108" t="s">
-        <v>1406</v>
+        <v>1412</v>
       </c>
       <c r="D33" s="108" t="n">
         <f aca="false">COUNTIFS(A36:A43,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="G33" s="108" t="s">
-        <v>1290</v>
+        <v>1294</v>
       </c>
       <c r="H33" s="108" t="n">
         <v>8</v>
       </c>
       <c r="I33" s="108" t="s">
-        <v>1406</v>
+        <v>1412</v>
       </c>
       <c r="J33" s="108" t="n">
         <f aca="false">COUNTIFS(A36:A43,"&lt;&gt;")</f>
@@ -24878,7 +25055,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="108" t="s">
-        <v>1407</v>
+        <v>1413</v>
       </c>
       <c r="B34" s="108" t="str">
         <f aca="false">_xlfn.TEXTJOIN(", ",TRUE(),IF(COUNTIF(B36:B43,"Bride")&gt;0,"Bride",""),IF(COUNTIF(B36:B43,"Groom")&gt;0,"Groom",""),IF(COUNTIF(B36:B43,"Both")&gt;0,"Both",""))</f>
@@ -24887,7 +25064,7 @@
       <c r="C34" s="108"/>
       <c r="D34" s="108"/>
       <c r="G34" s="108" t="s">
-        <v>1407</v>
+        <v>1413</v>
       </c>
       <c r="H34" s="108" t="str">
         <f aca="false">_xlfn.TEXTJOIN(", ",TRUE(),IF(COUNTIF(B36:B43,"Bride")&gt;0,"Bride",""),IF(COUNTIF(B36:B43,"Groom")&gt;0,"Groom",""),IF(COUNTIF(B36:B43,"Both")&gt;0,"Both",""))</f>
@@ -24901,20 +25078,20 @@
         <v>1249</v>
       </c>
       <c r="B35" s="77" t="s">
-        <v>1372</v>
+        <v>1378</v>
       </c>
       <c r="C35" s="77" t="s">
-        <v>1408</v>
+        <v>1414</v>
       </c>
       <c r="D35" s="77"/>
       <c r="G35" s="77" t="s">
         <v>1249</v>
       </c>
       <c r="H35" s="77" t="s">
-        <v>1372</v>
+        <v>1378</v>
       </c>
       <c r="I35" s="77" t="s">
-        <v>1408</v>
+        <v>1414</v>
       </c>
       <c r="J35" s="77"/>
     </row>
@@ -25080,13 +25257,13 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="107" t="s">
-        <v>1409</v>
+        <v>1415</v>
       </c>
       <c r="B49" s="107"/>
       <c r="C49" s="107"/>
       <c r="D49" s="107"/>
       <c r="G49" s="107" t="s">
-        <v>1410</v>
+        <v>1416</v>
       </c>
       <c r="H49" s="107"/>
       <c r="I49" s="107"/>
@@ -25094,26 +25271,26 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="108" t="s">
-        <v>1290</v>
+        <v>1294</v>
       </c>
       <c r="B50" s="108" t="n">
         <v>8</v>
       </c>
       <c r="C50" s="108" t="s">
-        <v>1406</v>
+        <v>1412</v>
       </c>
       <c r="D50" s="108" t="n">
         <f aca="false">COUNTIFS(A53:A60,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="G50" s="108" t="s">
-        <v>1290</v>
+        <v>1294</v>
       </c>
       <c r="H50" s="108" t="n">
         <v>8</v>
       </c>
       <c r="I50" s="108" t="s">
-        <v>1406</v>
+        <v>1412</v>
       </c>
       <c r="J50" s="108" t="n">
         <f aca="false">COUNTIFS(A53:A60,"&lt;&gt;")</f>
@@ -25122,7 +25299,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="108" t="s">
-        <v>1407</v>
+        <v>1413</v>
       </c>
       <c r="B51" s="108" t="str">
         <f aca="false">_xlfn.TEXTJOIN(", ",TRUE(),IF(COUNTIF(B53:B60,"Bride")&gt;0,"Bride",""),IF(COUNTIF(B53:B60,"Groom")&gt;0,"Groom",""),IF(COUNTIF(B53:B60,"Both")&gt;0,"Both",""))</f>
@@ -25131,7 +25308,7 @@
       <c r="C51" s="108"/>
       <c r="D51" s="108"/>
       <c r="G51" s="108" t="s">
-        <v>1407</v>
+        <v>1413</v>
       </c>
       <c r="H51" s="108" t="str">
         <f aca="false">_xlfn.TEXTJOIN(", ",TRUE(),IF(COUNTIF(B53:B60,"Bride")&gt;0,"Bride",""),IF(COUNTIF(B53:B60,"Groom")&gt;0,"Groom",""),IF(COUNTIF(B53:B60,"Both")&gt;0,"Both",""))</f>
@@ -25145,20 +25322,20 @@
         <v>1249</v>
       </c>
       <c r="B52" s="77" t="s">
-        <v>1372</v>
+        <v>1378</v>
       </c>
       <c r="C52" s="77" t="s">
-        <v>1408</v>
+        <v>1414</v>
       </c>
       <c r="D52" s="77"/>
       <c r="G52" s="77" t="s">
         <v>1249</v>
       </c>
       <c r="H52" s="77" t="s">
-        <v>1372</v>
+        <v>1378</v>
       </c>
       <c r="I52" s="77" t="s">
-        <v>1408</v>
+        <v>1414</v>
       </c>
       <c r="J52" s="77"/>
     </row>
@@ -25324,13 +25501,13 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="107" t="s">
-        <v>1411</v>
+        <v>1417</v>
       </c>
       <c r="B66" s="107"/>
       <c r="C66" s="107"/>
       <c r="D66" s="107"/>
       <c r="G66" s="107" t="s">
-        <v>1412</v>
+        <v>1418</v>
       </c>
       <c r="H66" s="107"/>
       <c r="I66" s="107"/>
@@ -25338,26 +25515,26 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="108" t="s">
-        <v>1290</v>
+        <v>1294</v>
       </c>
       <c r="B67" s="108" t="n">
         <v>8</v>
       </c>
       <c r="C67" s="108" t="s">
-        <v>1406</v>
+        <v>1412</v>
       </c>
       <c r="D67" s="108" t="n">
         <f aca="false">COUNTIFS(A70:A77,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="G67" s="108" t="s">
-        <v>1290</v>
+        <v>1294</v>
       </c>
       <c r="H67" s="108" t="n">
         <v>8</v>
       </c>
       <c r="I67" s="108" t="s">
-        <v>1406</v>
+        <v>1412</v>
       </c>
       <c r="J67" s="108" t="n">
         <f aca="false">COUNTIFS(A70:A77,"&lt;&gt;")</f>
@@ -25366,7 +25543,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="108" t="s">
-        <v>1407</v>
+        <v>1413</v>
       </c>
       <c r="B68" s="108" t="str">
         <f aca="false">_xlfn.TEXTJOIN(", ",TRUE(),IF(COUNTIF(B70:B77,"Bride")&gt;0,"Bride",""),IF(COUNTIF(B70:B77,"Groom")&gt;0,"Groom",""),IF(COUNTIF(B70:B77,"Both")&gt;0,"Both",""))</f>
@@ -25375,7 +25552,7 @@
       <c r="C68" s="108"/>
       <c r="D68" s="108"/>
       <c r="G68" s="108" t="s">
-        <v>1407</v>
+        <v>1413</v>
       </c>
       <c r="H68" s="108" t="str">
         <f aca="false">_xlfn.TEXTJOIN(", ",TRUE(),IF(COUNTIF(B70:B77,"Bride")&gt;0,"Bride",""),IF(COUNTIF(B70:B77,"Groom")&gt;0,"Groom",""),IF(COUNTIF(B70:B77,"Both")&gt;0,"Both",""))</f>
@@ -25389,20 +25566,20 @@
         <v>1249</v>
       </c>
       <c r="B69" s="77" t="s">
-        <v>1372</v>
+        <v>1378</v>
       </c>
       <c r="C69" s="77" t="s">
-        <v>1408</v>
+        <v>1414</v>
       </c>
       <c r="D69" s="77"/>
       <c r="G69" s="77" t="s">
         <v>1249</v>
       </c>
       <c r="H69" s="77" t="s">
-        <v>1372</v>
+        <v>1378</v>
       </c>
       <c r="I69" s="77" t="s">
-        <v>1408</v>
+        <v>1414</v>
       </c>
       <c r="J69" s="77"/>
     </row>
@@ -25568,13 +25745,13 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="107" t="s">
-        <v>1413</v>
+        <v>1419</v>
       </c>
       <c r="B83" s="107"/>
       <c r="C83" s="107"/>
       <c r="D83" s="107"/>
       <c r="G83" s="107" t="s">
-        <v>1414</v>
+        <v>1420</v>
       </c>
       <c r="H83" s="107"/>
       <c r="I83" s="107"/>
@@ -25582,26 +25759,26 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="108" t="s">
-        <v>1290</v>
+        <v>1294</v>
       </c>
       <c r="B84" s="108" t="n">
         <v>8</v>
       </c>
       <c r="C84" s="108" t="s">
-        <v>1406</v>
+        <v>1412</v>
       </c>
       <c r="D84" s="108" t="n">
         <f aca="false">COUNTIFS(A87:A94,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="G84" s="108" t="s">
-        <v>1290</v>
+        <v>1294</v>
       </c>
       <c r="H84" s="108" t="n">
         <v>8</v>
       </c>
       <c r="I84" s="108" t="s">
-        <v>1406</v>
+        <v>1412</v>
       </c>
       <c r="J84" s="108" t="n">
         <f aca="false">COUNTIFS(A87:A94,"&lt;&gt;")</f>
@@ -25610,7 +25787,7 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="108" t="s">
-        <v>1407</v>
+        <v>1413</v>
       </c>
       <c r="B85" s="108" t="str">
         <f aca="false">_xlfn.TEXTJOIN(", ",TRUE(),IF(COUNTIF(B87:B94,"Bride")&gt;0,"Bride",""),IF(COUNTIF(B87:B94,"Groom")&gt;0,"Groom",""),IF(COUNTIF(B87:B94,"Both")&gt;0,"Both",""))</f>
@@ -25619,7 +25796,7 @@
       <c r="C85" s="108"/>
       <c r="D85" s="108"/>
       <c r="G85" s="108" t="s">
-        <v>1407</v>
+        <v>1413</v>
       </c>
       <c r="H85" s="108" t="str">
         <f aca="false">_xlfn.TEXTJOIN(", ",TRUE(),IF(COUNTIF(B87:B94,"Bride")&gt;0,"Bride",""),IF(COUNTIF(B87:B94,"Groom")&gt;0,"Groom",""),IF(COUNTIF(B87:B94,"Both")&gt;0,"Both",""))</f>
@@ -25633,20 +25810,20 @@
         <v>1249</v>
       </c>
       <c r="B86" s="77" t="s">
-        <v>1372</v>
+        <v>1378</v>
       </c>
       <c r="C86" s="77" t="s">
-        <v>1408</v>
+        <v>1414</v>
       </c>
       <c r="D86" s="77"/>
       <c r="G86" s="77" t="s">
         <v>1249</v>
       </c>
       <c r="H86" s="77" t="s">
-        <v>1372</v>
+        <v>1378</v>
       </c>
       <c r="I86" s="77" t="s">
-        <v>1408</v>
+        <v>1414</v>
       </c>
       <c r="J86" s="77"/>
     </row>
@@ -25812,13 +25989,13 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="107" t="s">
-        <v>1415</v>
+        <v>1421</v>
       </c>
       <c r="B100" s="107"/>
       <c r="C100" s="107"/>
       <c r="D100" s="107"/>
       <c r="G100" s="107" t="s">
-        <v>1416</v>
+        <v>1422</v>
       </c>
       <c r="H100" s="107"/>
       <c r="I100" s="107"/>
@@ -25826,26 +26003,26 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="108" t="s">
-        <v>1290</v>
+        <v>1294</v>
       </c>
       <c r="B101" s="108" t="n">
         <v>8</v>
       </c>
       <c r="C101" s="108" t="s">
-        <v>1406</v>
+        <v>1412</v>
       </c>
       <c r="D101" s="108" t="n">
         <f aca="false">COUNTIFS(A104:A111,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="G101" s="108" t="s">
-        <v>1290</v>
+        <v>1294</v>
       </c>
       <c r="H101" s="108" t="n">
         <v>8</v>
       </c>
       <c r="I101" s="108" t="s">
-        <v>1406</v>
+        <v>1412</v>
       </c>
       <c r="J101" s="108" t="n">
         <f aca="false">COUNTIFS(A104:A111,"&lt;&gt;")</f>
@@ -25854,7 +26031,7 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="108" t="s">
-        <v>1407</v>
+        <v>1413</v>
       </c>
       <c r="B102" s="108" t="str">
         <f aca="false">_xlfn.TEXTJOIN(", ",TRUE(),IF(COUNTIF(B104:B111,"Bride")&gt;0,"Bride",""),IF(COUNTIF(B104:B111,"Groom")&gt;0,"Groom",""),IF(COUNTIF(B104:B111,"Both")&gt;0,"Both",""))</f>
@@ -25863,7 +26040,7 @@
       <c r="C102" s="108"/>
       <c r="D102" s="108"/>
       <c r="G102" s="108" t="s">
-        <v>1407</v>
+        <v>1413</v>
       </c>
       <c r="H102" s="108" t="str">
         <f aca="false">_xlfn.TEXTJOIN(", ",TRUE(),IF(COUNTIF(B104:B111,"Bride")&gt;0,"Bride",""),IF(COUNTIF(B104:B111,"Groom")&gt;0,"Groom",""),IF(COUNTIF(B104:B111,"Both")&gt;0,"Both",""))</f>
@@ -25877,20 +26054,20 @@
         <v>1249</v>
       </c>
       <c r="B103" s="77" t="s">
-        <v>1372</v>
+        <v>1378</v>
       </c>
       <c r="C103" s="77" t="s">
-        <v>1408</v>
+        <v>1414</v>
       </c>
       <c r="D103" s="77"/>
       <c r="G103" s="77" t="s">
         <v>1249</v>
       </c>
       <c r="H103" s="77" t="s">
-        <v>1372</v>
+        <v>1378</v>
       </c>
       <c r="I103" s="77" t="s">
-        <v>1408</v>
+        <v>1414</v>
       </c>
       <c r="J103" s="77"/>
     </row>
@@ -26109,7 +26286,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="73" t="s">
-        <v>1417</v>
+        <v>1423</v>
       </c>
       <c r="B1" s="73"/>
       <c r="C1" s="73"/>
@@ -26123,7 +26300,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="23" t="s">
-        <v>1395</v>
+        <v>1401</v>
       </c>
       <c r="B3" s="23"/>
       <c r="C3" s="23" t="s">
@@ -26131,19 +26308,19 @@
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23" t="s">
-        <v>1396</v>
+        <v>1402</v>
       </c>
       <c r="F3" s="23"/>
       <c r="G3" s="23" t="s">
-        <v>1397</v>
+        <v>1403</v>
       </c>
       <c r="H3" s="23"/>
       <c r="I3" s="23" t="s">
-        <v>1398</v>
+        <v>1404</v>
       </c>
       <c r="J3" s="23"/>
       <c r="K3" s="23" t="s">
-        <v>1399</v>
+        <v>1405</v>
       </c>
       <c r="L3" s="23"/>
     </row>
@@ -26181,7 +26358,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="62" t="s">
-        <v>1400</v>
+        <v>1406</v>
       </c>
       <c r="B6" s="62"/>
       <c r="C6" s="62"/>
@@ -26191,7 +26368,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="55" t="s">
-        <v>1401</v>
+        <v>1407</v>
       </c>
       <c r="B8" s="55"/>
       <c r="C8" s="55"/>
@@ -26202,13 +26379,13 @@
         <v>1249</v>
       </c>
       <c r="B9" s="56" t="s">
-        <v>1372</v>
+        <v>1378</v>
       </c>
       <c r="C9" s="56" t="s">
-        <v>1376</v>
+        <v>1382</v>
       </c>
       <c r="D9" s="56" t="s">
-        <v>1402</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26513,18 +26690,18 @@
     </row>
     <row r="31" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="106" t="s">
-        <v>1403</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="110" t="s">
-        <v>1404</v>
+        <v>1410</v>
       </c>
       <c r="B32" s="110"/>
       <c r="C32" s="110"/>
       <c r="D32" s="110"/>
       <c r="G32" s="110" t="s">
-        <v>1405</v>
+        <v>1411</v>
       </c>
       <c r="H32" s="110"/>
       <c r="I32" s="110"/>
@@ -26532,26 +26709,26 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="108" t="s">
-        <v>1290</v>
+        <v>1294</v>
       </c>
       <c r="B33" s="108" t="n">
         <v>8</v>
       </c>
       <c r="C33" s="108" t="s">
-        <v>1406</v>
+        <v>1412</v>
       </c>
       <c r="D33" s="108" t="n">
         <f aca="false">COUNTIFS(A36:A43,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="G33" s="108" t="s">
-        <v>1290</v>
+        <v>1294</v>
       </c>
       <c r="H33" s="108" t="n">
         <v>8</v>
       </c>
       <c r="I33" s="108" t="s">
-        <v>1406</v>
+        <v>1412</v>
       </c>
       <c r="J33" s="108" t="n">
         <f aca="false">COUNTIFS(A36:A43,"&lt;&gt;")</f>
@@ -26560,7 +26737,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="108" t="s">
-        <v>1407</v>
+        <v>1413</v>
       </c>
       <c r="B34" s="108" t="str">
         <f aca="false">_xlfn.TEXTJOIN(", ",TRUE(),IF(COUNTIF(B36:B43,"Bride")&gt;0,"Bride",""),IF(COUNTIF(B36:B43,"Groom")&gt;0,"Groom",""),IF(COUNTIF(B36:B43,"Both")&gt;0,"Both",""))</f>
@@ -26569,7 +26746,7 @@
       <c r="C34" s="108"/>
       <c r="D34" s="108"/>
       <c r="G34" s="108" t="s">
-        <v>1407</v>
+        <v>1413</v>
       </c>
       <c r="H34" s="108" t="str">
         <f aca="false">_xlfn.TEXTJOIN(", ",TRUE(),IF(COUNTIF(B36:B43,"Bride")&gt;0,"Bride",""),IF(COUNTIF(B36:B43,"Groom")&gt;0,"Groom",""),IF(COUNTIF(B36:B43,"Both")&gt;0,"Both",""))</f>
@@ -26583,20 +26760,20 @@
         <v>1249</v>
       </c>
       <c r="B35" s="74" t="s">
-        <v>1372</v>
+        <v>1378</v>
       </c>
       <c r="C35" s="74" t="s">
-        <v>1408</v>
+        <v>1414</v>
       </c>
       <c r="D35" s="74"/>
       <c r="G35" s="74" t="s">
         <v>1249</v>
       </c>
       <c r="H35" s="74" t="s">
-        <v>1372</v>
+        <v>1378</v>
       </c>
       <c r="I35" s="74" t="s">
-        <v>1408</v>
+        <v>1414</v>
       </c>
       <c r="J35" s="74"/>
     </row>
@@ -26762,13 +26939,13 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="110" t="s">
-        <v>1409</v>
+        <v>1415</v>
       </c>
       <c r="B49" s="110"/>
       <c r="C49" s="110"/>
       <c r="D49" s="110"/>
       <c r="G49" s="110" t="s">
-        <v>1410</v>
+        <v>1416</v>
       </c>
       <c r="H49" s="110"/>
       <c r="I49" s="110"/>
@@ -26776,26 +26953,26 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="108" t="s">
-        <v>1290</v>
+        <v>1294</v>
       </c>
       <c r="B50" s="108" t="n">
         <v>8</v>
       </c>
       <c r="C50" s="108" t="s">
-        <v>1406</v>
+        <v>1412</v>
       </c>
       <c r="D50" s="108" t="n">
         <f aca="false">COUNTIFS(A53:A60,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="G50" s="108" t="s">
-        <v>1290</v>
+        <v>1294</v>
       </c>
       <c r="H50" s="108" t="n">
         <v>8</v>
       </c>
       <c r="I50" s="108" t="s">
-        <v>1406</v>
+        <v>1412</v>
       </c>
       <c r="J50" s="108" t="n">
         <f aca="false">COUNTIFS(A53:A60,"&lt;&gt;")</f>
@@ -26804,7 +26981,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="108" t="s">
-        <v>1407</v>
+        <v>1413</v>
       </c>
       <c r="B51" s="108" t="str">
         <f aca="false">_xlfn.TEXTJOIN(", ",TRUE(),IF(COUNTIF(B53:B60,"Bride")&gt;0,"Bride",""),IF(COUNTIF(B53:B60,"Groom")&gt;0,"Groom",""),IF(COUNTIF(B53:B60,"Both")&gt;0,"Both",""))</f>
@@ -26813,7 +26990,7 @@
       <c r="C51" s="108"/>
       <c r="D51" s="108"/>
       <c r="G51" s="108" t="s">
-        <v>1407</v>
+        <v>1413</v>
       </c>
       <c r="H51" s="108" t="str">
         <f aca="false">_xlfn.TEXTJOIN(", ",TRUE(),IF(COUNTIF(B53:B60,"Bride")&gt;0,"Bride",""),IF(COUNTIF(B53:B60,"Groom")&gt;0,"Groom",""),IF(COUNTIF(B53:B60,"Both")&gt;0,"Both",""))</f>
@@ -26827,20 +27004,20 @@
         <v>1249</v>
       </c>
       <c r="B52" s="74" t="s">
-        <v>1372</v>
+        <v>1378</v>
       </c>
       <c r="C52" s="74" t="s">
-        <v>1408</v>
+        <v>1414</v>
       </c>
       <c r="D52" s="74"/>
       <c r="G52" s="74" t="s">
         <v>1249</v>
       </c>
       <c r="H52" s="74" t="s">
-        <v>1372</v>
+        <v>1378</v>
       </c>
       <c r="I52" s="74" t="s">
-        <v>1408</v>
+        <v>1414</v>
       </c>
       <c r="J52" s="74"/>
     </row>
@@ -27055,7 +27232,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="102" t="s">
-        <v>1418</v>
+        <v>1424</v>
       </c>
       <c r="B1" s="102"/>
       <c r="C1" s="102"/>
@@ -27070,25 +27247,25 @@
         <v>1153</v>
       </c>
       <c r="B3" s="79" t="s">
-        <v>1419</v>
+        <v>1425</v>
       </c>
       <c r="C3" s="79" t="s">
-        <v>1420</v>
+        <v>1426</v>
       </c>
       <c r="D3" s="79" t="s">
-        <v>1421</v>
+        <v>1427</v>
       </c>
       <c r="E3" s="79" t="s">
         <v>123</v>
       </c>
       <c r="F3" s="79" t="s">
-        <v>1422</v>
+        <v>1428</v>
       </c>
       <c r="G3" s="79" t="s">
-        <v>1423</v>
+        <v>1429</v>
       </c>
       <c r="H3" s="79" t="s">
-        <v>1424</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28230,7 +28407,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="61" t="s">
-        <v>1425</v>
+        <v>1431</v>
       </c>
       <c r="B1" s="61"/>
       <c r="C1" s="61"/>
@@ -28242,19 +28419,19 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="20" t="s">
-        <v>1426</v>
+        <v>1432</v>
       </c>
       <c r="B3" s="20"/>
       <c r="C3" s="20" t="s">
-        <v>1427</v>
+        <v>1433</v>
       </c>
       <c r="D3" s="20"/>
       <c r="E3" s="20" t="s">
-        <v>1428</v>
+        <v>1434</v>
       </c>
       <c r="F3" s="20"/>
       <c r="G3" s="20" t="s">
-        <v>1429</v>
+        <v>1435</v>
       </c>
       <c r="H3" s="20"/>
       <c r="J3" s="99" t="s">
@@ -28304,7 +28481,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="62" t="s">
-        <v>1430</v>
+        <v>1436</v>
       </c>
       <c r="B6" s="62"/>
       <c r="C6" s="62"/>
@@ -28338,7 +28515,7 @@
         <v>1249</v>
       </c>
       <c r="C8" s="63" t="s">
-        <v>1431</v>
+        <v>1437</v>
       </c>
       <c r="D8" s="63" t="s">
         <v>1250</v>
@@ -28347,7 +28524,7 @@
         <v>1251</v>
       </c>
       <c r="F8" s="63" t="s">
-        <v>1432</v>
+        <v>1438</v>
       </c>
       <c r="G8" s="63" t="s">
         <v>73</v>
@@ -28368,7 +28545,7 @@
         <v>100</v>
       </c>
       <c r="B9" s="57" t="s">
-        <v>1384</v>
+        <v>1390</v>
       </c>
       <c r="C9" s="57" t="s">
         <v>163</v>
@@ -28393,7 +28570,7 @@
         <v>100</v>
       </c>
       <c r="B10" s="59" t="s">
-        <v>1382</v>
+        <v>1388</v>
       </c>
       <c r="C10" s="59" t="s">
         <v>165</v>
@@ -28411,10 +28588,10 @@
         <v>100</v>
       </c>
       <c r="B11" s="57" t="s">
-        <v>1433</v>
+        <v>1439</v>
       </c>
       <c r="C11" s="57" t="s">
-        <v>1434</v>
+        <v>1440</v>
       </c>
       <c r="D11" s="57"/>
       <c r="E11" s="57"/>
@@ -28429,10 +28606,10 @@
         <v>100</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>1435</v>
+        <v>1441</v>
       </c>
       <c r="C12" s="59" t="s">
-        <v>1436</v>
+        <v>1442</v>
       </c>
       <c r="D12" s="59"/>
       <c r="E12" s="59"/>
@@ -28447,10 +28624,10 @@
         <v>100</v>
       </c>
       <c r="B13" s="57" t="s">
-        <v>1437</v>
+        <v>1443</v>
       </c>
       <c r="C13" s="57" t="s">
-        <v>1434</v>
+        <v>1440</v>
       </c>
       <c r="D13" s="57"/>
       <c r="E13" s="57"/>
@@ -28465,10 +28642,10 @@
         <v>100</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>1438</v>
+        <v>1444</v>
       </c>
       <c r="C14" s="59" t="s">
-        <v>1436</v>
+        <v>1442</v>
       </c>
       <c r="D14" s="59"/>
       <c r="E14" s="59"/>
@@ -28483,10 +28660,10 @@
         <v>100</v>
       </c>
       <c r="B15" s="57" t="s">
-        <v>1439</v>
+        <v>1445</v>
       </c>
       <c r="C15" s="57" t="s">
-        <v>1434</v>
+        <v>1440</v>
       </c>
       <c r="D15" s="57"/>
       <c r="E15" s="57"/>
@@ -28501,10 +28678,10 @@
         <v>336</v>
       </c>
       <c r="B16" s="59" t="s">
-        <v>1440</v>
+        <v>1446</v>
       </c>
       <c r="C16" s="59" t="s">
-        <v>1436</v>
+        <v>1442</v>
       </c>
       <c r="D16" s="59"/>
       <c r="E16" s="59"/>
@@ -28759,7 +28936,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="81" t="s">
-        <v>1441</v>
+        <v>1447</v>
       </c>
       <c r="B1" s="81"/>
       <c r="C1" s="81"/>
@@ -28767,23 +28944,23 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="71" t="s">
-        <v>1442</v>
+        <v>1448</v>
       </c>
       <c r="B3" s="71"/>
       <c r="C3" s="6" t="s">
-        <v>1443</v>
+        <v>1449</v>
       </c>
       <c r="D3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="79" t="s">
-        <v>1431</v>
+        <v>1437</v>
       </c>
       <c r="B4" s="79" t="s">
         <v>1249</v>
       </c>
       <c r="C4" s="52" t="s">
-        <v>1431</v>
+        <v>1437</v>
       </c>
       <c r="D4" s="52" t="s">
         <v>1249</v>
@@ -28863,7 +29040,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="55" t="s">
-        <v>1444</v>
+        <v>1450</v>
       </c>
       <c r="B19" s="55"/>
       <c r="C19" s="55"/>
@@ -30095,7 +30272,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="73" t="s">
-        <v>1445</v>
+        <v>1451</v>
       </c>
       <c r="B1" s="73"/>
       <c r="C1" s="73"/>
@@ -30108,7 +30285,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="23" t="s">
-        <v>1446</v>
+        <v>1452</v>
       </c>
       <c r="B3" s="23"/>
       <c r="C3" s="23" t="s">
@@ -30116,19 +30293,19 @@
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23" t="s">
-        <v>1447</v>
+        <v>1453</v>
       </c>
       <c r="F3" s="23"/>
       <c r="G3" s="23" t="s">
-        <v>1448</v>
+        <v>1454</v>
       </c>
       <c r="H3" s="23"/>
       <c r="I3" s="23" t="s">
-        <v>1449</v>
+        <v>1455</v>
       </c>
       <c r="J3" s="23"/>
       <c r="K3" s="23" t="s">
-        <v>1450</v>
+        <v>1456</v>
       </c>
       <c r="L3" s="23"/>
     </row>
@@ -30166,34 +30343,34 @@
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="74" t="s">
-        <v>1431</v>
+        <v>1437</v>
       </c>
       <c r="B6" s="74" t="s">
-        <v>1451</v>
+        <v>1457</v>
       </c>
       <c r="C6" s="74" t="s">
-        <v>1419</v>
+        <v>1425</v>
       </c>
       <c r="D6" s="74" t="s">
-        <v>1420</v>
+        <v>1426</v>
       </c>
       <c r="E6" s="74" t="s">
-        <v>1452</v>
+        <v>1458</v>
       </c>
       <c r="F6" s="74" t="s">
+        <v>1314</v>
+      </c>
+      <c r="G6" s="74" t="s">
         <v>1308</v>
-      </c>
-      <c r="G6" s="74" t="s">
-        <v>1302</v>
       </c>
       <c r="H6" s="74" t="s">
         <v>1237</v>
       </c>
       <c r="I6" s="74" t="s">
-        <v>1453</v>
+        <v>1459</v>
       </c>
       <c r="J6" s="74" t="s">
-        <v>1454</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30212,7 +30389,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="57" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="I7" s="67" t="s">
         <v>336</v>
@@ -30235,7 +30412,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="59" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="I8" s="65" t="s">
         <v>336</v>
@@ -30258,7 +30435,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="57" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="I9" s="67" t="s">
         <v>336</v>
@@ -30281,7 +30458,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="59" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="I10" s="65" t="s">
         <v>336</v>
@@ -30304,7 +30481,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="57" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="I11" s="67" t="s">
         <v>336</v>
@@ -30327,7 +30504,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="59" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="I12" s="65" t="s">
         <v>336</v>
@@ -30350,7 +30527,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="57" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="I13" s="67" t="s">
         <v>336</v>
@@ -30373,7 +30550,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="59" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="I14" s="65" t="s">
         <v>336</v>
@@ -30396,7 +30573,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="57" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="I15" s="67" t="s">
         <v>336</v>
@@ -30419,7 +30596,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="59" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="I16" s="65" t="s">
         <v>336</v>
@@ -30442,7 +30619,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="57" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="I17" s="67" t="s">
         <v>336</v>
@@ -30465,7 +30642,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="59" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="I18" s="65" t="s">
         <v>336</v>
@@ -30488,7 +30665,7 @@
         <v>0</v>
       </c>
       <c r="H19" s="57" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="I19" s="67" t="s">
         <v>336</v>
@@ -30511,7 +30688,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="59" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="I20" s="65" t="s">
         <v>336</v>
@@ -30534,7 +30711,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="57" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="I21" s="67" t="s">
         <v>336</v>
@@ -30557,7 +30734,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="59" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="I22" s="65" t="s">
         <v>336</v>
@@ -30580,7 +30757,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="57" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="I23" s="67" t="s">
         <v>336</v>
@@ -30603,7 +30780,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="59" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="I24" s="65" t="s">
         <v>336</v>
@@ -30626,7 +30803,7 @@
         <v>0</v>
       </c>
       <c r="H25" s="57" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="I25" s="67" t="s">
         <v>336</v>
@@ -30649,7 +30826,7 @@
         <v>0</v>
       </c>
       <c r="H26" s="59" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="I26" s="65" t="s">
         <v>336</v>
@@ -30719,7 +30896,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="114" t="s">
-        <v>1456</v>
+        <v>1462</v>
       </c>
       <c r="B1" s="114"/>
       <c r="C1" s="114"/>
@@ -30729,7 +30906,7 @@
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="115" t="s">
-        <v>1457</v>
+        <v>1463</v>
       </c>
       <c r="B3" s="115"/>
       <c r="C3" s="115"/>
@@ -30787,15 +30964,15 @@
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="116" t="s">
-        <v>1458</v>
+        <v>1464</v>
       </c>
       <c r="B11" s="116"/>
       <c r="C11" s="116" t="s">
-        <v>1458</v>
+        <v>1464</v>
       </c>
       <c r="D11" s="116"/>
       <c r="E11" s="116" t="s">
-        <v>1458</v>
+        <v>1464</v>
       </c>
       <c r="F11" s="116"/>
     </row>
@@ -30849,15 +31026,15 @@
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="116" t="s">
-        <v>1458</v>
+        <v>1464</v>
       </c>
       <c r="B19" s="116"/>
       <c r="C19" s="116" t="s">
-        <v>1458</v>
+        <v>1464</v>
       </c>
       <c r="D19" s="116"/>
       <c r="E19" s="116" t="s">
-        <v>1458</v>
+        <v>1464</v>
       </c>
       <c r="F19" s="116"/>
     </row>
@@ -30912,7 +31089,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="75" t="s">
-        <v>1459</v>
+        <v>1465</v>
       </c>
       <c r="B1" s="75"/>
       <c r="C1" s="75"/>
@@ -30927,7 +31104,7 @@
         <v>1002</v>
       </c>
       <c r="AE2" s="0" t="s">
-        <v>1460</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30936,15 +31113,15 @@
       </c>
       <c r="B3" s="22"/>
       <c r="C3" s="22" t="s">
-        <v>1369</v>
+        <v>1375</v>
       </c>
       <c r="D3" s="22"/>
       <c r="E3" s="22" t="s">
-        <v>1461</v>
+        <v>1467</v>
       </c>
       <c r="F3" s="22"/>
       <c r="G3" s="22" t="s">
-        <v>1462</v>
+        <v>1468</v>
       </c>
       <c r="H3" s="22"/>
       <c r="AD3" s="19" t="s">
@@ -30986,7 +31163,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD5" s="0" t="s">
-        <v>1463</v>
+        <v>1469</v>
       </c>
       <c r="AE5" s="0" t="n">
         <f aca="false">SUMIFS($H$7:$H$46,$B$7:$B$46,AD5,$D$7:$D$46,"Confirmed")</f>
@@ -30998,31 +31175,31 @@
         <v>1153</v>
       </c>
       <c r="B6" s="77" t="s">
-        <v>1464</v>
+        <v>1470</v>
       </c>
       <c r="C6" s="77" t="s">
-        <v>1465</v>
+        <v>1471</v>
       </c>
       <c r="D6" s="77" t="s">
         <v>1237</v>
       </c>
       <c r="E6" s="77" t="s">
-        <v>1466</v>
+        <v>1472</v>
       </c>
       <c r="F6" s="77" t="s">
-        <v>1452</v>
+        <v>1458</v>
       </c>
       <c r="G6" s="77" t="s">
-        <v>1467</v>
+        <v>1473</v>
       </c>
       <c r="H6" s="77" t="s">
-        <v>1302</v>
+        <v>1308</v>
       </c>
       <c r="I6" s="77" t="s">
-        <v>1468</v>
+        <v>1474</v>
       </c>
       <c r="AD6" s="19" t="s">
-        <v>1469</v>
+        <v>1475</v>
       </c>
       <c r="AE6" s="19" t="n">
         <f aca="false">SUMIFS($H$7:$H$46,$B$7:$B$46,AD6,$D$7:$D$46,"Confirmed")</f>
@@ -31031,19 +31208,19 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="57" t="s">
-        <v>1470</v>
+        <v>1476</v>
       </c>
       <c r="B7" s="57" t="s">
         <v>1024</v>
       </c>
       <c r="C7" s="57" t="s">
-        <v>1471</v>
+        <v>1477</v>
       </c>
       <c r="D7" s="57" t="s">
         <v>1259</v>
       </c>
       <c r="E7" s="57" t="s">
-        <v>1472</v>
+        <v>1478</v>
       </c>
       <c r="F7" s="86" t="n">
         <v>350</v>
@@ -31057,7 +31234,7 @@
       </c>
       <c r="I7" s="57"/>
       <c r="AD7" s="19" t="s">
-        <v>1473</v>
+        <v>1479</v>
       </c>
       <c r="AE7" s="19" t="n">
         <f aca="false">SUMIFS($H$7:$H$46,$B$7:$B$46,AD7,$D$7:$D$46,"Confirmed")</f>
@@ -31066,19 +31243,19 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>1474</v>
+        <v>1480</v>
       </c>
       <c r="B8" s="59" t="s">
         <v>1024</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>1475</v>
+        <v>1481</v>
       </c>
       <c r="D8" s="59" t="s">
         <v>1259</v>
       </c>
       <c r="E8" s="59" t="s">
-        <v>1472</v>
+        <v>1478</v>
       </c>
       <c r="F8" s="87" t="n">
         <v>18</v>
@@ -31092,7 +31269,7 @@
       </c>
       <c r="I8" s="59"/>
       <c r="AD8" s="19" t="s">
-        <v>1476</v>
+        <v>1482</v>
       </c>
       <c r="AE8" s="19" t="n">
         <f aca="false">SUMIFS($H$7:$H$46,$B$7:$B$46,AD8,$D$7:$D$46,"Confirmed")</f>
@@ -31101,19 +31278,19 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="57" t="s">
-        <v>1477</v>
+        <v>1483</v>
       </c>
       <c r="B9" s="57" t="s">
-        <v>1463</v>
+        <v>1469</v>
       </c>
       <c r="C9" s="57" t="s">
-        <v>1478</v>
+        <v>1484</v>
       </c>
       <c r="D9" s="57" t="s">
         <v>1259</v>
       </c>
       <c r="E9" s="57" t="s">
-        <v>1479</v>
+        <v>1485</v>
       </c>
       <c r="F9" s="86" t="n">
         <v>90</v>
@@ -31127,7 +31304,7 @@
       </c>
       <c r="I9" s="57"/>
       <c r="AD9" s="19" t="s">
-        <v>1480</v>
+        <v>1486</v>
       </c>
       <c r="AE9" s="19" t="n">
         <f aca="false">SUMIFS($H$7:$H$46,$B$7:$B$46,AD9,$D$7:$D$46,"Confirmed")</f>
@@ -31136,19 +31313,19 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="59" t="s">
-        <v>1481</v>
+        <v>1487</v>
       </c>
       <c r="B10" s="59" t="s">
-        <v>1469</v>
+        <v>1475</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>1471</v>
+        <v>1477</v>
       </c>
       <c r="D10" s="59" t="s">
         <v>1259</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>1472</v>
+        <v>1478</v>
       </c>
       <c r="F10" s="87" t="n">
         <v>45</v>
@@ -31162,7 +31339,7 @@
       </c>
       <c r="I10" s="59"/>
       <c r="AD10" s="19" t="s">
-        <v>1482</v>
+        <v>1488</v>
       </c>
       <c r="AE10" s="19" t="n">
         <f aca="false">SUMIFS($H$7:$H$46,$B$7:$B$46,AD10,$D$7:$D$46,"Confirmed")</f>
@@ -31171,19 +31348,19 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="57" t="s">
-        <v>1483</v>
+        <v>1489</v>
       </c>
       <c r="B11" s="57" t="s">
-        <v>1469</v>
+        <v>1475</v>
       </c>
       <c r="C11" s="57" t="s">
-        <v>1484</v>
+        <v>1490</v>
       </c>
       <c r="D11" s="57" t="s">
         <v>1259</v>
       </c>
       <c r="E11" s="57" t="s">
-        <v>1472</v>
+        <v>1478</v>
       </c>
       <c r="F11" s="86" t="n">
         <v>12</v>
@@ -31206,19 +31383,19 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="59" t="s">
-        <v>1485</v>
+        <v>1491</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>1473</v>
+        <v>1479</v>
       </c>
       <c r="C12" s="59" t="s">
-        <v>1471</v>
+        <v>1477</v>
       </c>
       <c r="D12" s="59" t="s">
-        <v>1486</v>
+        <v>1492</v>
       </c>
       <c r="E12" s="59" t="s">
-        <v>1472</v>
+        <v>1478</v>
       </c>
       <c r="F12" s="87" t="n">
         <v>220</v>
@@ -31234,19 +31411,19 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="57" t="s">
-        <v>1487</v>
+        <v>1493</v>
       </c>
       <c r="B13" s="57" t="s">
-        <v>1469</v>
+        <v>1475</v>
       </c>
       <c r="C13" s="57" t="s">
-        <v>1475</v>
+        <v>1481</v>
       </c>
       <c r="D13" s="57" t="s">
         <v>1259</v>
       </c>
       <c r="E13" s="57" t="s">
-        <v>1472</v>
+        <v>1478</v>
       </c>
       <c r="F13" s="86" t="n">
         <v>8</v>
@@ -31262,19 +31439,19 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="59" t="s">
-        <v>1488</v>
+        <v>1494</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>1469</v>
+        <v>1475</v>
       </c>
       <c r="C14" s="59" t="s">
-        <v>1478</v>
+        <v>1484</v>
       </c>
       <c r="D14" s="59" t="s">
-        <v>1486</v>
+        <v>1492</v>
       </c>
       <c r="E14" s="59" t="s">
-        <v>1479</v>
+        <v>1485</v>
       </c>
       <c r="F14" s="87" t="n">
         <v>3</v>
@@ -31293,7 +31470,7 @@
       <c r="B15" s="57"/>
       <c r="C15" s="57"/>
       <c r="D15" s="57" t="s">
-        <v>1486</v>
+        <v>1492</v>
       </c>
       <c r="E15" s="57"/>
       <c r="F15" s="86" t="n">
@@ -31313,7 +31490,7 @@
       <c r="B16" s="59"/>
       <c r="C16" s="59"/>
       <c r="D16" s="59" t="s">
-        <v>1486</v>
+        <v>1492</v>
       </c>
       <c r="E16" s="59"/>
       <c r="F16" s="87" t="n">
@@ -31333,7 +31510,7 @@
       <c r="B17" s="57"/>
       <c r="C17" s="57"/>
       <c r="D17" s="57" t="s">
-        <v>1486</v>
+        <v>1492</v>
       </c>
       <c r="E17" s="57"/>
       <c r="F17" s="86" t="n">
@@ -31353,7 +31530,7 @@
       <c r="B18" s="59"/>
       <c r="C18" s="59"/>
       <c r="D18" s="59" t="s">
-        <v>1486</v>
+        <v>1492</v>
       </c>
       <c r="E18" s="59"/>
       <c r="F18" s="87" t="n">
@@ -31373,7 +31550,7 @@
       <c r="B19" s="57"/>
       <c r="C19" s="57"/>
       <c r="D19" s="57" t="s">
-        <v>1486</v>
+        <v>1492</v>
       </c>
       <c r="E19" s="57"/>
       <c r="F19" s="86" t="n">
@@ -31393,7 +31570,7 @@
       <c r="B20" s="59"/>
       <c r="C20" s="59"/>
       <c r="D20" s="59" t="s">
-        <v>1486</v>
+        <v>1492</v>
       </c>
       <c r="E20" s="59"/>
       <c r="F20" s="87" t="n">
@@ -31413,7 +31590,7 @@
       <c r="B21" s="57"/>
       <c r="C21" s="57"/>
       <c r="D21" s="57" t="s">
-        <v>1486</v>
+        <v>1492</v>
       </c>
       <c r="E21" s="57"/>
       <c r="F21" s="86" t="n">
@@ -31433,7 +31610,7 @@
       <c r="B22" s="59"/>
       <c r="C22" s="59"/>
       <c r="D22" s="59" t="s">
-        <v>1486</v>
+        <v>1492</v>
       </c>
       <c r="E22" s="59"/>
       <c r="F22" s="87" t="n">
@@ -31453,7 +31630,7 @@
       <c r="B23" s="57"/>
       <c r="C23" s="57"/>
       <c r="D23" s="57" t="s">
-        <v>1486</v>
+        <v>1492</v>
       </c>
       <c r="E23" s="57"/>
       <c r="F23" s="86" t="n">
@@ -31473,7 +31650,7 @@
       <c r="B24" s="59"/>
       <c r="C24" s="59"/>
       <c r="D24" s="59" t="s">
-        <v>1486</v>
+        <v>1492</v>
       </c>
       <c r="E24" s="59"/>
       <c r="F24" s="87" t="n">
@@ -31493,7 +31670,7 @@
       <c r="B25" s="57"/>
       <c r="C25" s="57"/>
       <c r="D25" s="57" t="s">
-        <v>1486</v>
+        <v>1492</v>
       </c>
       <c r="E25" s="57"/>
       <c r="F25" s="86" t="n">
@@ -31513,7 +31690,7 @@
       <c r="B26" s="59"/>
       <c r="C26" s="59"/>
       <c r="D26" s="59" t="s">
-        <v>1486</v>
+        <v>1492</v>
       </c>
       <c r="E26" s="59"/>
       <c r="F26" s="87" t="n">
@@ -31533,7 +31710,7 @@
       <c r="B27" s="57"/>
       <c r="C27" s="57"/>
       <c r="D27" s="57" t="s">
-        <v>1486</v>
+        <v>1492</v>
       </c>
       <c r="E27" s="57"/>
       <c r="F27" s="86" t="n">
@@ -31553,7 +31730,7 @@
       <c r="B28" s="59"/>
       <c r="C28" s="59"/>
       <c r="D28" s="59" t="s">
-        <v>1486</v>
+        <v>1492</v>
       </c>
       <c r="E28" s="59"/>
       <c r="F28" s="87" t="n">
@@ -31573,7 +31750,7 @@
       <c r="B29" s="57"/>
       <c r="C29" s="57"/>
       <c r="D29" s="57" t="s">
-        <v>1486</v>
+        <v>1492</v>
       </c>
       <c r="E29" s="57"/>
       <c r="F29" s="86" t="n">
@@ -31593,7 +31770,7 @@
       <c r="B30" s="59"/>
       <c r="C30" s="59"/>
       <c r="D30" s="59" t="s">
-        <v>1486</v>
+        <v>1492</v>
       </c>
       <c r="E30" s="59"/>
       <c r="F30" s="87" t="n">
@@ -31613,7 +31790,7 @@
       <c r="B31" s="57"/>
       <c r="C31" s="57"/>
       <c r="D31" s="57" t="s">
-        <v>1486</v>
+        <v>1492</v>
       </c>
       <c r="E31" s="57"/>
       <c r="F31" s="86" t="n">
@@ -31633,7 +31810,7 @@
       <c r="B32" s="59"/>
       <c r="C32" s="59"/>
       <c r="D32" s="59" t="s">
-        <v>1486</v>
+        <v>1492</v>
       </c>
       <c r="E32" s="59"/>
       <c r="F32" s="87" t="n">
@@ -31653,7 +31830,7 @@
       <c r="B33" s="57"/>
       <c r="C33" s="57"/>
       <c r="D33" s="57" t="s">
-        <v>1486</v>
+        <v>1492</v>
       </c>
       <c r="E33" s="57"/>
       <c r="F33" s="86" t="n">
@@ -31673,7 +31850,7 @@
       <c r="B34" s="59"/>
       <c r="C34" s="59"/>
       <c r="D34" s="59" t="s">
-        <v>1486</v>
+        <v>1492</v>
       </c>
       <c r="E34" s="59"/>
       <c r="F34" s="87" t="n">
@@ -31693,7 +31870,7 @@
       <c r="B35" s="57"/>
       <c r="C35" s="57"/>
       <c r="D35" s="57" t="s">
-        <v>1486</v>
+        <v>1492</v>
       </c>
       <c r="E35" s="57"/>
       <c r="F35" s="86" t="n">
@@ -31713,7 +31890,7 @@
       <c r="B36" s="59"/>
       <c r="C36" s="59"/>
       <c r="D36" s="59" t="s">
-        <v>1486</v>
+        <v>1492</v>
       </c>
       <c r="E36" s="59"/>
       <c r="F36" s="87" t="n">
@@ -31733,7 +31910,7 @@
       <c r="B37" s="57"/>
       <c r="C37" s="57"/>
       <c r="D37" s="57" t="s">
-        <v>1486</v>
+        <v>1492</v>
       </c>
       <c r="E37" s="57"/>
       <c r="F37" s="86" t="n">
@@ -31753,7 +31930,7 @@
       <c r="B38" s="59"/>
       <c r="C38" s="59"/>
       <c r="D38" s="59" t="s">
-        <v>1486</v>
+        <v>1492</v>
       </c>
       <c r="E38" s="59"/>
       <c r="F38" s="87" t="n">
@@ -31773,7 +31950,7 @@
       <c r="B39" s="57"/>
       <c r="C39" s="57"/>
       <c r="D39" s="57" t="s">
-        <v>1486</v>
+        <v>1492</v>
       </c>
       <c r="E39" s="57"/>
       <c r="F39" s="86" t="n">
@@ -31793,7 +31970,7 @@
       <c r="B40" s="59"/>
       <c r="C40" s="59"/>
       <c r="D40" s="59" t="s">
-        <v>1486</v>
+        <v>1492</v>
       </c>
       <c r="E40" s="59"/>
       <c r="F40" s="87" t="n">
@@ -31813,7 +31990,7 @@
       <c r="B41" s="57"/>
       <c r="C41" s="57"/>
       <c r="D41" s="57" t="s">
-        <v>1486</v>
+        <v>1492</v>
       </c>
       <c r="E41" s="57"/>
       <c r="F41" s="86" t="n">
@@ -31833,7 +32010,7 @@
       <c r="B42" s="59"/>
       <c r="C42" s="59"/>
       <c r="D42" s="59" t="s">
-        <v>1486</v>
+        <v>1492</v>
       </c>
       <c r="E42" s="59"/>
       <c r="F42" s="87" t="n">
@@ -31853,7 +32030,7 @@
       <c r="B43" s="57"/>
       <c r="C43" s="57"/>
       <c r="D43" s="57" t="s">
-        <v>1486</v>
+        <v>1492</v>
       </c>
       <c r="E43" s="57"/>
       <c r="F43" s="86" t="n">
@@ -31873,7 +32050,7 @@
       <c r="B44" s="59"/>
       <c r="C44" s="59"/>
       <c r="D44" s="59" t="s">
-        <v>1486</v>
+        <v>1492</v>
       </c>
       <c r="E44" s="59"/>
       <c r="F44" s="87" t="n">
@@ -31893,7 +32070,7 @@
       <c r="B45" s="57"/>
       <c r="C45" s="57"/>
       <c r="D45" s="57" t="s">
-        <v>1486</v>
+        <v>1492</v>
       </c>
       <c r="E45" s="57"/>
       <c r="F45" s="86" t="n">
@@ -31913,7 +32090,7 @@
       <c r="B46" s="59"/>
       <c r="C46" s="59"/>
       <c r="D46" s="59" t="s">
-        <v>1486</v>
+        <v>1492</v>
       </c>
       <c r="E46" s="59"/>
       <c r="F46" s="87" t="n">
@@ -31997,7 +32174,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="102" t="s">
-        <v>1489</v>
+        <v>1495</v>
       </c>
       <c r="B1" s="102"/>
       <c r="C1" s="102"/>
@@ -32009,7 +32186,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="21" t="s">
-        <v>1490</v>
+        <v>1496</v>
       </c>
       <c r="B3" s="21"/>
       <c r="C3" s="21"/>
@@ -32041,30 +32218,30 @@
         <v>1222</v>
       </c>
       <c r="C6" s="79" t="s">
-        <v>1452</v>
+        <v>1458</v>
       </c>
       <c r="D6" s="79" t="s">
-        <v>1467</v>
+        <v>1473</v>
       </c>
       <c r="E6" s="79" t="s">
-        <v>1302</v>
+        <v>1308</v>
       </c>
       <c r="F6" s="79" t="s">
         <v>1237</v>
       </c>
       <c r="G6" s="79" t="s">
-        <v>1491</v>
+        <v>1497</v>
       </c>
       <c r="H6" s="79" t="s">
         <v>1155</v>
       </c>
       <c r="I6" s="79" t="s">
-        <v>1468</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="57" t="s">
-        <v>1492</v>
+        <v>1498</v>
       </c>
       <c r="B7" s="57"/>
       <c r="C7" s="86" t="n">
@@ -32086,7 +32263,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>1493</v>
+        <v>1499</v>
       </c>
       <c r="B8" s="59"/>
       <c r="C8" s="87" t="n">
@@ -32108,7 +32285,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="57" t="s">
-        <v>1494</v>
+        <v>1500</v>
       </c>
       <c r="B9" s="57"/>
       <c r="C9" s="86" t="n">
@@ -32130,7 +32307,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="59" t="s">
-        <v>1495</v>
+        <v>1501</v>
       </c>
       <c r="B10" s="59"/>
       <c r="C10" s="87" t="n">
@@ -32152,7 +32329,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="57" t="s">
-        <v>1496</v>
+        <v>1502</v>
       </c>
       <c r="B11" s="57"/>
       <c r="C11" s="86" t="n">
@@ -32174,7 +32351,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="59" t="s">
-        <v>1361</v>
+        <v>1367</v>
       </c>
       <c r="B12" s="59"/>
       <c r="C12" s="87" t="n">
@@ -32196,7 +32373,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="57" t="s">
-        <v>1497</v>
+        <v>1503</v>
       </c>
       <c r="B13" s="57"/>
       <c r="C13" s="86" t="n">
@@ -32218,7 +32395,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="59" t="s">
-        <v>1498</v>
+        <v>1504</v>
       </c>
       <c r="B14" s="59"/>
       <c r="C14" s="87" t="n">
@@ -32729,7 +32906,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="81" t="s">
-        <v>1499</v>
+        <v>1505</v>
       </c>
       <c r="B1" s="81"/>
       <c r="C1" s="81"/>
@@ -32737,7 +32914,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="55" t="s">
-        <v>1500</v>
+        <v>1506</v>
       </c>
       <c r="B3" s="55"/>
       <c r="C3" s="55"/>
@@ -32748,7 +32925,7 @@
         <v>1000</v>
       </c>
       <c r="B4" s="56" t="s">
-        <v>1501</v>
+        <v>1507</v>
       </c>
       <c r="C4" s="56" t="s">
         <v>1214</v>
@@ -32758,40 +32935,88 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="57"/>
-      <c r="B5" s="57"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
+      <c r="A5" s="57" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B5" s="57" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="57" t="s">
+        <v>1509</v>
+      </c>
+      <c r="D5" s="57" t="s">
+        <v>1510</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="59"/>
-      <c r="B6" s="59"/>
-      <c r="C6" s="59"/>
-      <c r="D6" s="59"/>
+      <c r="A6" s="59" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B6" s="59" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="59" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D6" s="59" t="s">
+        <v>1511</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="57"/>
-      <c r="B7" s="57"/>
-      <c r="C7" s="57"/>
-      <c r="D7" s="57"/>
+      <c r="A7" s="57" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B7" s="57" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="57" t="s">
+        <v>1512</v>
+      </c>
+      <c r="D7" s="57" t="s">
+        <v>1513</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="59"/>
-      <c r="B8" s="59"/>
-      <c r="C8" s="59"/>
-      <c r="D8" s="59"/>
+      <c r="A8" s="59" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B8" s="59" t="s">
+        <v>1514</v>
+      </c>
+      <c r="C8" s="59" t="s">
+        <v>1509</v>
+      </c>
+      <c r="D8" s="59" t="s">
+        <v>1515</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="57"/>
-      <c r="B9" s="57"/>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
+      <c r="A9" s="57" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B9" s="57" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C9" s="57" t="s">
+        <v>1512</v>
+      </c>
+      <c r="D9" s="57" t="s">
+        <v>1516</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="59"/>
-      <c r="B10" s="59"/>
-      <c r="C10" s="59"/>
-      <c r="D10" s="59"/>
+      <c r="A10" s="59" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B10" s="59" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="59" t="s">
+        <v>1517</v>
+      </c>
+      <c r="D10" s="59" t="s">
+        <v>1518</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="57"/>
@@ -32819,7 +33044,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>1502</v>
+        <v>1519</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -32828,13 +33053,13 @@
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="52" t="s">
-        <v>1468</v>
+        <v>1474</v>
       </c>
       <c r="B18" s="52" t="s">
         <v>1000</v>
       </c>
       <c r="C18" s="52" t="s">
-        <v>1501</v>
+        <v>1507</v>
       </c>
       <c r="D18" s="52" t="s">
         <v>1214</v>
@@ -32990,7 +33215,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="118" t="s">
-        <v>1503</v>
+        <v>1520</v>
       </c>
       <c r="B1" s="118"/>
       <c r="C1" s="118"/>
@@ -32999,16 +33224,16 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="55" t="s">
-        <v>1504</v>
+        <v>1521</v>
       </c>
       <c r="B3" s="55"/>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="56" t="s">
-        <v>1505</v>
+        <v>1522</v>
       </c>
       <c r="B4" s="56" t="s">
-        <v>1506</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33313,7 +33538,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>1507</v>
+        <v>1524</v>
       </c>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -33322,19 +33547,19 @@
     </row>
     <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="52" t="s">
-        <v>1508</v>
+        <v>1525</v>
       </c>
       <c r="B37" s="52" t="s">
-        <v>1509</v>
+        <v>1526</v>
       </c>
       <c r="C37" s="52" t="s">
-        <v>1510</v>
+        <v>1527</v>
       </c>
       <c r="D37" s="52" t="s">
-        <v>1511</v>
+        <v>1528</v>
       </c>
       <c r="E37" s="52" t="s">
-        <v>1512</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33594,7 +33819,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="121" t="s">
-        <v>1513</v>
+        <v>1530</v>
       </c>
       <c r="B1" s="121"/>
       <c r="C1" s="121"/>
@@ -33606,69 +33831,129 @@
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="77" t="s">
-        <v>1514</v>
+        <v>1531</v>
       </c>
       <c r="B3" s="77" t="s">
         <v>1235</v>
       </c>
       <c r="C3" s="77" t="s">
-        <v>1515</v>
+        <v>1532</v>
       </c>
       <c r="D3" s="77" t="s">
-        <v>1516</v>
+        <v>1533</v>
       </c>
       <c r="E3" s="77" t="s">
-        <v>1517</v>
+        <v>1534</v>
       </c>
       <c r="F3" s="77" t="s">
-        <v>1518</v>
+        <v>1535</v>
       </c>
       <c r="G3" s="77" t="s">
-        <v>1519</v>
+        <v>1536</v>
       </c>
       <c r="H3" s="77" t="s">
         <v>1155</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="57"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="58"/>
+      <c r="A4" s="57" t="s">
+        <v>1537</v>
+      </c>
+      <c r="B4" s="57" t="s">
+        <v>1538</v>
+      </c>
+      <c r="C4" s="57" t="s">
+        <v>1539</v>
+      </c>
+      <c r="D4" s="57" t="s">
+        <v>1540</v>
+      </c>
+      <c r="E4" s="57" t="s">
+        <v>1239</v>
+      </c>
+      <c r="F4" s="58" t="n">
+        <f aca="false">'Get Started'!$C$4</f>
+        <v>46552</v>
+      </c>
       <c r="G4" s="122"/>
-      <c r="H4" s="57"/>
+      <c r="H4" s="57" t="s">
+        <v>1541</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="59"/>
-      <c r="B5" s="59"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="60"/>
+      <c r="A5" s="59" t="s">
+        <v>1542</v>
+      </c>
+      <c r="B5" s="59" t="s">
+        <v>1543</v>
+      </c>
+      <c r="C5" s="59" t="s">
+        <v>1544</v>
+      </c>
+      <c r="D5" s="59" t="s">
+        <v>1545</v>
+      </c>
+      <c r="E5" s="59" t="s">
+        <v>1239</v>
+      </c>
+      <c r="F5" s="60" t="n">
+        <f aca="false">'Get Started'!$C$4</f>
+        <v>46552</v>
+      </c>
       <c r="G5" s="123"/>
-      <c r="H5" s="59"/>
+      <c r="H5" s="59" t="s">
+        <v>1546</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="57"/>
-      <c r="B6" s="57"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="58"/>
+      <c r="A6" s="57" t="s">
+        <v>1547</v>
+      </c>
+      <c r="B6" s="57" t="s">
+        <v>1538</v>
+      </c>
+      <c r="C6" s="57" t="s">
+        <v>1539</v>
+      </c>
+      <c r="D6" s="57" t="s">
+        <v>1548</v>
+      </c>
+      <c r="E6" s="57" t="s">
+        <v>1239</v>
+      </c>
+      <c r="F6" s="58" t="n">
+        <f aca="false">'Get Started'!$C$4</f>
+        <v>46552</v>
+      </c>
       <c r="G6" s="122"/>
-      <c r="H6" s="57"/>
+      <c r="H6" s="57" t="s">
+        <v>1549</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="59"/>
-      <c r="B7" s="59"/>
-      <c r="C7" s="59"/>
-      <c r="D7" s="59"/>
-      <c r="E7" s="59"/>
-      <c r="F7" s="60"/>
+      <c r="A7" s="59" t="s">
+        <v>1550</v>
+      </c>
+      <c r="B7" s="59" t="s">
+        <v>1551</v>
+      </c>
+      <c r="C7" s="59" t="s">
+        <v>1552</v>
+      </c>
+      <c r="D7" s="59" t="s">
+        <v>1239</v>
+      </c>
+      <c r="E7" s="59" t="s">
+        <v>1553</v>
+      </c>
+      <c r="F7" s="60" t="n">
+        <f aca="false">'Get Started'!$C$4</f>
+        <v>46552</v>
+      </c>
       <c r="G7" s="123"/>
-      <c r="H7" s="59"/>
+      <c r="H7" s="59" t="s">
+        <v>1554</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="57"/>
@@ -33873,7 +34158,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="124" t="s">
-        <v>1520</v>
+        <v>1555</v>
       </c>
       <c r="B1" s="124"/>
       <c r="C1" s="124"/>
@@ -33887,7 +34172,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD2" s="0" t="s">
-        <v>1521</v>
+        <v>1556</v>
       </c>
       <c r="AE2" s="0" t="s">
         <v>130</v>
@@ -33895,7 +34180,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="25" t="s">
-        <v>1522</v>
+        <v>1557</v>
       </c>
       <c r="B3" s="25"/>
       <c r="AD3" s="19" t="s">
@@ -33913,7 +34198,7 @@
       </c>
       <c r="B4" s="105"/>
       <c r="AD4" s="19" t="s">
-        <v>1523</v>
+        <v>1558</v>
       </c>
       <c r="AE4" s="19" t="n">
         <f aca="false">COUNTIF($D$7:$D$26,AD4)</f>
@@ -33922,7 +34207,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD5" s="0" t="s">
-        <v>1524</v>
+        <v>1559</v>
       </c>
       <c r="AE5" s="0" t="n">
         <f aca="false">COUNTIF($D$7:$D$26,AD5)</f>
@@ -33934,51 +34219,51 @@
         <v>1214</v>
       </c>
       <c r="B6" s="56" t="s">
-        <v>1525</v>
+        <v>1560</v>
       </c>
       <c r="C6" s="56" t="s">
-        <v>1467</v>
+        <v>1473</v>
       </c>
       <c r="D6" s="56" t="s">
-        <v>1521</v>
+        <v>1556</v>
       </c>
       <c r="E6" s="56" t="s">
-        <v>1526</v>
+        <v>1561</v>
       </c>
       <c r="F6" s="56" t="s">
-        <v>1527</v>
+        <v>1562</v>
       </c>
       <c r="G6" s="56" t="s">
-        <v>1528</v>
+        <v>1563</v>
       </c>
       <c r="H6" s="56" t="s">
         <v>113</v>
       </c>
       <c r="I6" s="56" t="s">
-        <v>1529</v>
+        <v>1564</v>
       </c>
       <c r="J6" s="56" t="s">
-        <v>1530</v>
+        <v>1565</v>
       </c>
       <c r="K6" s="56" t="s">
-        <v>1302</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="57" t="s">
-        <v>1531</v>
+        <v>1566</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>1532</v>
+        <v>1567</v>
       </c>
       <c r="C7" s="57" t="n">
         <v>80</v>
       </c>
       <c r="D7" s="57" t="s">
-        <v>1524</v>
+        <v>1559</v>
       </c>
       <c r="E7" s="57" t="s">
-        <v>1533</v>
+        <v>1568</v>
       </c>
       <c r="F7" s="67" t="s">
         <v>336</v>
@@ -33996,7 +34281,7 @@
         <v>156</v>
       </c>
       <c r="AD7" s="19" t="s">
-        <v>1534</v>
+        <v>1569</v>
       </c>
       <c r="AE7" s="19" t="s">
         <v>130</v>
@@ -34004,16 +34289,16 @@
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>1531</v>
+        <v>1566</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>1535</v>
+        <v>1570</v>
       </c>
       <c r="C8" s="59" t="n">
         <v>80</v>
       </c>
       <c r="D8" s="59" t="s">
-        <v>1524</v>
+        <v>1559</v>
       </c>
       <c r="E8" s="59" t="s">
         <v>75</v>
@@ -34034,7 +34319,7 @@
         <v>400</v>
       </c>
       <c r="AD8" s="19" t="s">
-        <v>1536</v>
+        <v>1571</v>
       </c>
       <c r="AE8" s="19" t="n">
         <f aca="false">COUNTIF($E$7:$E$26,AD8)</f>
@@ -34043,19 +34328,19 @@
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="57" t="s">
-        <v>1531</v>
+        <v>1566</v>
       </c>
       <c r="B9" s="57" t="s">
-        <v>1537</v>
+        <v>1572</v>
       </c>
       <c r="C9" s="57" t="n">
         <v>80</v>
       </c>
       <c r="D9" s="57" t="s">
-        <v>1523</v>
+        <v>1558</v>
       </c>
       <c r="E9" s="57" t="s">
-        <v>1538</v>
+        <v>1573</v>
       </c>
       <c r="F9" s="67" t="s">
         <v>336</v>
@@ -34073,7 +34358,7 @@
         <v>104</v>
       </c>
       <c r="AD9" s="19" t="s">
-        <v>1538</v>
+        <v>1573</v>
       </c>
       <c r="AE9" s="19" t="n">
         <f aca="false">COUNTIF($E$7:$E$26,AD9)</f>
@@ -34082,19 +34367,19 @@
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="59" t="s">
-        <v>1539</v>
+        <v>1508</v>
       </c>
       <c r="B10" s="59" t="s">
-        <v>1540</v>
+        <v>1574</v>
       </c>
       <c r="C10" s="59" t="n">
         <v>60</v>
       </c>
       <c r="D10" s="59" t="s">
-        <v>1523</v>
+        <v>1558</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>1538</v>
+        <v>1573</v>
       </c>
       <c r="F10" s="65" t="s">
         <v>336</v>
@@ -34121,10 +34406,10 @@
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="57" t="s">
-        <v>1539</v>
+        <v>1508</v>
       </c>
       <c r="B11" s="57" t="s">
-        <v>1541</v>
+        <v>1575</v>
       </c>
       <c r="C11" s="57" t="n">
         <v>60</v>
@@ -34133,7 +34418,7 @@
         <v>74</v>
       </c>
       <c r="E11" s="57" t="s">
-        <v>1538</v>
+        <v>1573</v>
       </c>
       <c r="F11" s="67" t="s">
         <v>336</v>
@@ -34151,7 +34436,7 @@
         <v>0</v>
       </c>
       <c r="AD11" s="19" t="s">
-        <v>1533</v>
+        <v>1568</v>
       </c>
       <c r="AE11" s="19" t="n">
         <f aca="false">COUNTIF($E$7:$E$26,AD11)</f>
@@ -34160,10 +34445,10 @@
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="59" t="s">
-        <v>1539</v>
+        <v>1508</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>1542</v>
+        <v>1576</v>
       </c>
       <c r="C12" s="59" t="n">
         <v>80</v>
@@ -34172,7 +34457,7 @@
         <v>74</v>
       </c>
       <c r="E12" s="59" t="s">
-        <v>1538</v>
+        <v>1573</v>
       </c>
       <c r="F12" s="65" t="s">
         <v>336</v>
@@ -34192,19 +34477,19 @@
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="57" t="s">
-        <v>1539</v>
+        <v>1508</v>
       </c>
       <c r="B13" s="57" t="s">
-        <v>1543</v>
+        <v>1577</v>
       </c>
       <c r="C13" s="57" t="n">
         <v>15</v>
       </c>
       <c r="D13" s="57" t="s">
-        <v>1524</v>
+        <v>1559</v>
       </c>
       <c r="E13" s="57" t="s">
-        <v>1533</v>
+        <v>1568</v>
       </c>
       <c r="F13" s="67" t="s">
         <v>336</v>
@@ -34230,19 +34515,19 @@
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="59" t="s">
-        <v>1539</v>
+        <v>1508</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>1544</v>
+        <v>1578</v>
       </c>
       <c r="C14" s="59" t="n">
         <v>1</v>
       </c>
       <c r="D14" s="59" t="s">
-        <v>1523</v>
+        <v>1558</v>
       </c>
       <c r="E14" s="59" t="s">
-        <v>1538</v>
+        <v>1573</v>
       </c>
       <c r="F14" s="65" t="s">
         <v>336</v>
@@ -34260,7 +34545,7 @@
         <v>45</v>
       </c>
       <c r="AD14" s="19" t="s">
-        <v>1531</v>
+        <v>1566</v>
       </c>
       <c r="AE14" s="19" t="n">
         <f aca="false">SUMIFS($K$7:$K$26,$A$7:$A$26,AD14)</f>
@@ -34269,10 +34554,10 @@
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="57" t="s">
-        <v>1545</v>
+        <v>1579</v>
       </c>
       <c r="B15" s="57" t="s">
-        <v>1546</v>
+        <v>1580</v>
       </c>
       <c r="C15" s="57" t="n">
         <v>80</v>
@@ -34281,7 +34566,7 @@
         <v>74</v>
       </c>
       <c r="E15" s="57" t="s">
-        <v>1536</v>
+        <v>1571</v>
       </c>
       <c r="F15" s="67" t="s">
         <v>336</v>
@@ -34299,7 +34584,7 @@
         <v>0</v>
       </c>
       <c r="AD15" s="19" t="s">
-        <v>1539</v>
+        <v>1508</v>
       </c>
       <c r="AE15" s="19" t="n">
         <f aca="false">SUMIFS($K$7:$K$26,$A$7:$A$26,AD15)</f>
@@ -34308,19 +34593,19 @@
     </row>
     <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="59" t="s">
-        <v>1539</v>
+        <v>1508</v>
       </c>
       <c r="B16" s="59" t="s">
-        <v>1547</v>
+        <v>1581</v>
       </c>
       <c r="C16" s="59" t="n">
         <v>1</v>
       </c>
       <c r="D16" s="59" t="s">
-        <v>1524</v>
+        <v>1559</v>
       </c>
       <c r="E16" s="59" t="s">
-        <v>1533</v>
+        <v>1568</v>
       </c>
       <c r="F16" s="65" t="s">
         <v>336</v>
@@ -34338,7 +34623,7 @@
         <v>55</v>
       </c>
       <c r="AD16" s="19" t="s">
-        <v>1545</v>
+        <v>1579</v>
       </c>
       <c r="AE16" s="19" t="n">
         <f aca="false">SUMIFS($K$7:$K$26,$A$7:$A$26,AD16)</f>
@@ -34355,7 +34640,7 @@
         <v>74</v>
       </c>
       <c r="E17" s="57" t="s">
-        <v>1538</v>
+        <v>1573</v>
       </c>
       <c r="F17" s="67" t="s">
         <v>336</v>
@@ -34383,7 +34668,7 @@
         <v>74</v>
       </c>
       <c r="E18" s="59" t="s">
-        <v>1538</v>
+        <v>1573</v>
       </c>
       <c r="F18" s="65" t="s">
         <v>336</v>
@@ -34411,7 +34696,7 @@
         <v>74</v>
       </c>
       <c r="E19" s="57" t="s">
-        <v>1538</v>
+        <v>1573</v>
       </c>
       <c r="F19" s="67" t="s">
         <v>336</v>
@@ -34439,7 +34724,7 @@
         <v>74</v>
       </c>
       <c r="E20" s="59" t="s">
-        <v>1538</v>
+        <v>1573</v>
       </c>
       <c r="F20" s="65" t="s">
         <v>336</v>
@@ -34467,7 +34752,7 @@
         <v>74</v>
       </c>
       <c r="E21" s="57" t="s">
-        <v>1538</v>
+        <v>1573</v>
       </c>
       <c r="F21" s="67" t="s">
         <v>336</v>
@@ -34495,7 +34780,7 @@
         <v>74</v>
       </c>
       <c r="E22" s="59" t="s">
-        <v>1538</v>
+        <v>1573</v>
       </c>
       <c r="F22" s="65" t="s">
         <v>336</v>
@@ -34523,7 +34808,7 @@
         <v>74</v>
       </c>
       <c r="E23" s="57" t="s">
-        <v>1538</v>
+        <v>1573</v>
       </c>
       <c r="F23" s="67" t="s">
         <v>336</v>
@@ -34551,7 +34836,7 @@
         <v>74</v>
       </c>
       <c r="E24" s="59" t="s">
-        <v>1538</v>
+        <v>1573</v>
       </c>
       <c r="F24" s="65" t="s">
         <v>336</v>
@@ -34579,7 +34864,7 @@
         <v>74</v>
       </c>
       <c r="E25" s="57" t="s">
-        <v>1538</v>
+        <v>1573</v>
       </c>
       <c r="F25" s="67" t="s">
         <v>336</v>
@@ -34607,7 +34892,7 @@
         <v>74</v>
       </c>
       <c r="E26" s="59" t="s">
-        <v>1538</v>
+        <v>1573</v>
       </c>
       <c r="F26" s="65" t="s">
         <v>336</v>
@@ -34692,7 +34977,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="125" t="s">
-        <v>1374</v>
+        <v>1380</v>
       </c>
       <c r="B1" s="125"/>
       <c r="C1" s="125"/>
@@ -34702,7 +34987,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="115" t="s">
-        <v>1548</v>
+        <v>1582</v>
       </c>
       <c r="B3" s="115"/>
       <c r="C3" s="115"/>
@@ -34808,21 +35093,21 @@
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="126" t="s">
-        <v>1549</v>
+        <v>1583</v>
       </c>
       <c r="B17" s="126"/>
       <c r="C17" s="126" t="s">
-        <v>1550</v>
+        <v>1584</v>
       </c>
       <c r="D17" s="126"/>
       <c r="E17" s="126" t="s">
-        <v>1551</v>
+        <v>1585</v>
       </c>
       <c r="F17" s="126"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="55" t="s">
-        <v>1552</v>
+        <v>1586</v>
       </c>
       <c r="B19" s="55"/>
       <c r="C19" s="55"/>
@@ -34832,7 +35117,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="127" t="s">
-        <v>1553</v>
+        <v>1587</v>
       </c>
       <c r="B20" s="127"/>
       <c r="C20" s="127"/>
@@ -34866,7 +35151,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="55" t="s">
-        <v>1554</v>
+        <v>1588</v>
       </c>
       <c r="B25" s="55"/>
       <c r="C25" s="55"/>
@@ -34876,7 +35161,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="127" t="s">
-        <v>1555</v>
+        <v>1589</v>
       </c>
       <c r="B26" s="127"/>
       <c r="C26" s="127"/>
@@ -34949,7 +35234,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="128" t="s">
-        <v>1556</v>
+        <v>1590</v>
       </c>
       <c r="B1" s="128"/>
       <c r="C1" s="128"/>
@@ -34973,7 +35258,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="129" t="s">
-        <v>1557</v>
+        <v>1591</v>
       </c>
       <c r="B4" s="130"/>
       <c r="C4" s="129" t="s">
@@ -34985,7 +35270,7 @@
       </c>
       <c r="F4" s="130"/>
       <c r="G4" s="129" t="s">
-        <v>1558</v>
+        <v>1592</v>
       </c>
       <c r="H4" s="130"/>
     </row>
@@ -34999,7 +35284,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>1559</v>
+        <v>1593</v>
       </c>
       <c r="B7" s="21"/>
       <c r="C7" s="21" t="s">
@@ -35067,7 +35352,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="59" t="s">
-        <v>1297</v>
+        <v>1303</v>
       </c>
       <c r="B13" s="87" t="n">
         <v>0</v>
@@ -35097,7 +35382,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="59" t="s">
-        <v>1560</v>
+        <v>1594</v>
       </c>
       <c r="B15" s="87" t="n">
         <v>0</v>
@@ -35159,7 +35444,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="71" t="s">
-        <v>1561</v>
+        <v>1595</v>
       </c>
       <c r="B20" s="71"/>
       <c r="C20" s="71"/>
@@ -35169,7 +35454,7 @@
         <v>1249</v>
       </c>
       <c r="B21" s="79" t="s">
-        <v>1376</v>
+        <v>1382</v>
       </c>
       <c r="C21" s="79" t="s">
         <v>1155</v>
@@ -36529,7 +36814,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="121" t="s">
-        <v>1562</v>
+        <v>1596</v>
       </c>
       <c r="B1" s="121"/>
       <c r="C1" s="121"/>
@@ -36553,7 +36838,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="129" t="s">
-        <v>1557</v>
+        <v>1591</v>
       </c>
       <c r="B4" s="130"/>
       <c r="C4" s="129" t="s">
@@ -36565,7 +36850,7 @@
       </c>
       <c r="F4" s="130"/>
       <c r="G4" s="129" t="s">
-        <v>1558</v>
+        <v>1592</v>
       </c>
       <c r="H4" s="130"/>
     </row>
@@ -36579,7 +36864,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="22" t="s">
-        <v>1559</v>
+        <v>1593</v>
       </c>
       <c r="B7" s="22"/>
       <c r="C7" s="22" t="s">
@@ -36647,7 +36932,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="59" t="s">
-        <v>1297</v>
+        <v>1303</v>
       </c>
       <c r="B13" s="87" t="n">
         <v>0</v>
@@ -36677,7 +36962,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="59" t="s">
-        <v>1563</v>
+        <v>1597</v>
       </c>
       <c r="B15" s="87" t="n">
         <v>0</v>
@@ -36739,7 +37024,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="76" t="s">
-        <v>1561</v>
+        <v>1595</v>
       </c>
       <c r="B20" s="76"/>
       <c r="C20" s="76"/>
@@ -36749,7 +37034,7 @@
         <v>1249</v>
       </c>
       <c r="B21" s="77" t="s">
-        <v>1376</v>
+        <v>1382</v>
       </c>
       <c r="C21" s="77" t="s">
         <v>1155</v>
@@ -36935,7 +37220,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="132" t="s">
-        <v>1564</v>
+        <v>1598</v>
       </c>
       <c r="B1" s="132"/>
       <c r="C1" s="132"/>
@@ -36962,14 +37247,14 @@
         <v>1234</v>
       </c>
       <c r="B4" s="130" t="s">
-        <v>1565</v>
+        <v>1599</v>
       </c>
       <c r="C4" s="129" t="s">
-        <v>1566</v>
+        <v>1600</v>
       </c>
       <c r="D4" s="130"/>
       <c r="E4" s="129" t="s">
-        <v>1567</v>
+        <v>1601</v>
       </c>
       <c r="F4" s="130"/>
       <c r="G4" s="129" t="s">
@@ -37003,27 +37288,27 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="80" t="s">
-        <v>1561</v>
+        <v>1595</v>
       </c>
       <c r="B9" s="80"/>
       <c r="C9" s="80"/>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="56" t="s">
-        <v>1568</v>
+        <v>1602</v>
       </c>
       <c r="B10" s="56"/>
       <c r="C10" s="56"/>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="56" t="s">
-        <v>1557</v>
+        <v>1591</v>
       </c>
       <c r="B11" s="56" t="s">
         <v>999</v>
       </c>
       <c r="C11" s="56" t="s">
-        <v>1569</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37083,7 +37368,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="133" t="s">
-        <v>1570</v>
+        <v>1604</v>
       </c>
       <c r="B23" s="133"/>
       <c r="C23" s="133"/>
@@ -37096,19 +37381,19 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="52" t="s">
-        <v>1571</v>
+        <v>1605</v>
       </c>
       <c r="B24" s="52" t="s">
         <v>1249</v>
       </c>
       <c r="C24" s="52" t="s">
-        <v>1572</v>
+        <v>1606</v>
       </c>
       <c r="D24" s="52" t="s">
         <v>1251</v>
       </c>
       <c r="E24" s="52" t="s">
-        <v>1573</v>
+        <v>1607</v>
       </c>
       <c r="F24" s="52" t="s">
         <v>1133</v>
@@ -37117,15 +37402,15 @@
         <v>1237</v>
       </c>
       <c r="H24" s="52" t="s">
-        <v>1574</v>
+        <v>1608</v>
       </c>
       <c r="I24" s="52" t="s">
-        <v>1575</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="57" t="s">
-        <v>1576</v>
+        <v>1610</v>
       </c>
       <c r="B25" s="57"/>
       <c r="C25" s="57"/>
@@ -37138,7 +37423,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="59" t="s">
-        <v>1577</v>
+        <v>1611</v>
       </c>
       <c r="B26" s="59"/>
       <c r="C26" s="59"/>
@@ -37156,7 +37441,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="134" t="s">
-        <v>1578</v>
+        <v>1612</v>
       </c>
       <c r="B28" s="134"/>
       <c r="C28" s="134"/>
@@ -37166,19 +37451,19 @@
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="77" t="s">
-        <v>1579</v>
+        <v>1613</v>
       </c>
       <c r="B29" s="77" t="s">
-        <v>1580</v>
+        <v>1614</v>
       </c>
       <c r="C29" s="77" t="s">
-        <v>1581</v>
+        <v>1615</v>
       </c>
       <c r="D29" s="77" t="s">
-        <v>1582</v>
+        <v>1616</v>
       </c>
       <c r="E29" s="77" t="s">
-        <v>1583</v>
+        <v>1617</v>
       </c>
       <c r="F29" s="77" t="s">
         <v>1155</v>
@@ -37250,7 +37535,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="71" t="s">
-        <v>1584</v>
+        <v>1618</v>
       </c>
       <c r="B39" s="71"/>
       <c r="C39" s="71"/>
@@ -37258,7 +37543,7 @@
     </row>
     <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="79" t="s">
-        <v>1557</v>
+        <v>1591</v>
       </c>
       <c r="B40" s="79" t="s">
         <v>1207</v>
@@ -37267,7 +37552,7 @@
         <v>1214</v>
       </c>
       <c r="D40" s="79" t="s">
-        <v>1454</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37384,7 +37669,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="57" t="s">
-        <v>1585</v>
+        <v>1619</v>
       </c>
       <c r="B59" s="86" t="n">
         <v>0</v>
@@ -37399,7 +37684,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="59" t="s">
-        <v>1586</v>
+        <v>1620</v>
       </c>
       <c r="B60" s="87" t="n">
         <v>0</v>
@@ -37414,7 +37699,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="57" t="s">
-        <v>1587</v>
+        <v>1621</v>
       </c>
       <c r="B61" s="86" t="n">
         <v>0</v>
@@ -37429,7 +37714,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="59" t="s">
-        <v>1297</v>
+        <v>1303</v>
       </c>
       <c r="B62" s="87" t="n">
         <v>0</v>
@@ -37444,7 +37729,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="57" t="s">
-        <v>1432</v>
+        <v>1438</v>
       </c>
       <c r="B63" s="86" t="n">
         <v>0</v>
@@ -37551,7 +37836,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="43" t="s">
-        <v>1588</v>
+        <v>1622</v>
       </c>
       <c r="B1" s="43"/>
       <c r="C1" s="43"/>
@@ -37586,7 +37871,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>1589</v>
+        <v>1623</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -37608,7 +37893,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="57" t="s">
-        <v>1590</v>
+        <v>1624</v>
       </c>
       <c r="B8" s="86" t="n">
         <v>0</v>
@@ -37623,7 +37908,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="59" t="s">
-        <v>1585</v>
+        <v>1619</v>
       </c>
       <c r="B9" s="87" t="n">
         <v>0</v>
@@ -37638,7 +37923,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="57" t="s">
-        <v>1297</v>
+        <v>1303</v>
       </c>
       <c r="B10" s="86" t="n">
         <v>0</v>
@@ -37653,7 +37938,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="59" t="s">
-        <v>1591</v>
+        <v>1625</v>
       </c>
       <c r="B11" s="87" t="n">
         <v>0</v>
@@ -37668,7 +37953,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="57" t="s">
-        <v>1592</v>
+        <v>1626</v>
       </c>
       <c r="B12" s="86" t="n">
         <v>0</v>
@@ -37730,7 +38015,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="55" t="s">
-        <v>1593</v>
+        <v>1627</v>
       </c>
       <c r="B17" s="55"/>
       <c r="C17" s="55"/>
@@ -37739,27 +38024,27 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="129" t="s">
-        <v>1594</v>
+        <v>1628</v>
       </c>
       <c r="B18" s="129" t="s">
-        <v>1595</v>
+        <v>1629</v>
       </c>
       <c r="C18" s="129" t="s">
-        <v>1596</v>
+        <v>1630</v>
       </c>
       <c r="D18" s="129" t="s">
         <v>1207</v>
       </c>
       <c r="E18" s="129" t="s">
-        <v>1597</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="130" t="s">
-        <v>1598</v>
+        <v>1632</v>
       </c>
       <c r="B19" s="130" t="s">
-        <v>1599</v>
+        <v>1633</v>
       </c>
       <c r="C19" s="130" t="n">
         <v>0.92</v>
@@ -37774,7 +38059,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="76" t="s">
-        <v>1600</v>
+        <v>1634</v>
       </c>
       <c r="B22" s="76"/>
       <c r="C22" s="76"/>
@@ -37782,7 +38067,7 @@
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="77" t="s">
-        <v>1557</v>
+        <v>1591</v>
       </c>
       <c r="B23" s="77" t="s">
         <v>1207</v>
@@ -37791,7 +38076,7 @@
         <v>1214</v>
       </c>
       <c r="D23" s="77" t="s">
-        <v>1454</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37916,7 +38201,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="71" t="s">
-        <v>1570</v>
+        <v>1604</v>
       </c>
       <c r="B45" s="71"/>
       <c r="C45" s="71"/>
@@ -37928,19 +38213,19 @@
     </row>
     <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="79" t="s">
-        <v>1571</v>
+        <v>1605</v>
       </c>
       <c r="B46" s="79" t="s">
         <v>1249</v>
       </c>
       <c r="C46" s="79" t="s">
-        <v>1572</v>
+        <v>1606</v>
       </c>
       <c r="D46" s="79" t="s">
         <v>1251</v>
       </c>
       <c r="E46" s="79" t="s">
-        <v>1573</v>
+        <v>1607</v>
       </c>
       <c r="F46" s="79" t="s">
         <v>1133</v>
@@ -37949,12 +38234,12 @@
         <v>1237</v>
       </c>
       <c r="H46" s="79" t="s">
-        <v>1575</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="113" t="s">
-        <v>1576</v>
+        <v>1610</v>
       </c>
       <c r="B47" s="113"/>
       <c r="C47" s="113"/>
@@ -37966,7 +38251,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="135" t="s">
-        <v>1577</v>
+        <v>1611</v>
       </c>
       <c r="B48" s="135"/>
       <c r="C48" s="135"/>
@@ -37978,7 +38263,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="80" t="s">
-        <v>1578</v>
+        <v>1612</v>
       </c>
       <c r="B50" s="80"/>
       <c r="C50" s="80"/>
@@ -37988,19 +38273,19 @@
     </row>
     <row r="51" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="74" t="s">
-        <v>1579</v>
+        <v>1613</v>
       </c>
       <c r="B51" s="74" t="s">
-        <v>1580</v>
+        <v>1614</v>
       </c>
       <c r="C51" s="74" t="s">
-        <v>1581</v>
+        <v>1615</v>
       </c>
       <c r="D51" s="74" t="s">
-        <v>1582</v>
+        <v>1616</v>
       </c>
       <c r="E51" s="74" t="s">
-        <v>1583</v>
+        <v>1617</v>
       </c>
       <c r="F51" s="74" t="s">
         <v>1155</v>
@@ -38056,7 +38341,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="64" t="s">
-        <v>1601</v>
+        <v>1635</v>
       </c>
       <c r="B60" s="64"/>
       <c r="C60" s="64"/>
@@ -38081,7 +38366,7 @@
         <v>122</v>
       </c>
       <c r="J61" s="99" t="s">
-        <v>1602</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38089,7 +38374,7 @@
         <v>336</v>
       </c>
       <c r="B62" s="57" t="s">
-        <v>1603</v>
+        <v>1637</v>
       </c>
       <c r="C62" s="57" t="s">
         <v>67</v>
@@ -38114,13 +38399,13 @@
         <v>336</v>
       </c>
       <c r="B63" s="59" t="s">
-        <v>1604</v>
+        <v>1638</v>
       </c>
       <c r="C63" s="59" t="s">
         <v>67</v>
       </c>
       <c r="F63" s="19" t="s">
-        <v>1602</v>
+        <v>1636</v>
       </c>
       <c r="G63" s="19" t="n">
         <f aca="false">COUNTIF(A62:A71,UnchkVal)</f>
@@ -38139,7 +38424,7 @@
         <v>336</v>
       </c>
       <c r="B64" s="57" t="s">
-        <v>1605</v>
+        <v>1639</v>
       </c>
       <c r="C64" s="57" t="s">
         <v>67</v>
@@ -38157,7 +38442,7 @@
         <v>336</v>
       </c>
       <c r="B65" s="59" t="s">
-        <v>1606</v>
+        <v>1640</v>
       </c>
       <c r="C65" s="59" t="s">
         <v>67</v>
@@ -38175,7 +38460,7 @@
         <v>336</v>
       </c>
       <c r="B66" s="57" t="s">
-        <v>1607</v>
+        <v>1641</v>
       </c>
       <c r="C66" s="57" t="s">
         <v>67</v>
@@ -38193,7 +38478,7 @@
         <v>336</v>
       </c>
       <c r="B67" s="59" t="s">
-        <v>1608</v>
+        <v>1642</v>
       </c>
       <c r="C67" s="59" t="s">
         <v>67</v>
@@ -38211,7 +38496,7 @@
         <v>336</v>
       </c>
       <c r="B68" s="57" t="s">
-        <v>1609</v>
+        <v>1643</v>
       </c>
       <c r="C68" s="57" t="s">
         <v>67</v>
@@ -38229,7 +38514,7 @@
         <v>336</v>
       </c>
       <c r="B69" s="59" t="s">
-        <v>1610</v>
+        <v>1644</v>
       </c>
       <c r="C69" s="59" t="s">
         <v>67</v>
@@ -38247,7 +38532,7 @@
         <v>336</v>
       </c>
       <c r="B70" s="57" t="s">
-        <v>1611</v>
+        <v>1645</v>
       </c>
       <c r="C70" s="57" t="s">
         <v>67</v>
@@ -38258,7 +38543,7 @@
         <v>336</v>
       </c>
       <c r="B71" s="59" t="s">
-        <v>1612</v>
+        <v>1646</v>
       </c>
       <c r="C71" s="59" t="s">
         <v>67</v>
@@ -38266,7 +38551,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="142" t="s">
-        <v>1613</v>
+        <v>1647</v>
       </c>
     </row>
   </sheetData>
@@ -38343,7 +38628,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="75" t="s">
-        <v>1614</v>
+        <v>1648</v>
       </c>
       <c r="B1" s="75"/>
       <c r="C1" s="75"/>
@@ -38353,7 +38638,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="22" t="s">
-        <v>1615</v>
+        <v>1649</v>
       </c>
       <c r="B3" s="22"/>
       <c r="C3" s="22"/>
@@ -38368,19 +38653,19 @@
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="77" t="s">
-        <v>1508</v>
+        <v>1525</v>
       </c>
       <c r="B6" s="77" t="s">
-        <v>1616</v>
+        <v>1650</v>
       </c>
       <c r="C6" s="77" t="s">
-        <v>1617</v>
+        <v>1651</v>
       </c>
       <c r="D6" s="77" t="s">
-        <v>1618</v>
+        <v>1652</v>
       </c>
       <c r="E6" s="77" t="s">
-        <v>1619</v>
+        <v>1653</v>
       </c>
       <c r="F6" s="77" t="s">
         <v>1155</v>
@@ -40827,91 +41112,91 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="99" t="s">
-        <v>1620</v>
+        <v>1654</v>
       </c>
       <c r="B1" s="99" t="s">
         <v>123</v>
       </c>
       <c r="C1" s="99" t="s">
-        <v>1621</v>
+        <v>1655</v>
       </c>
       <c r="D1" s="99" t="s">
-        <v>1622</v>
+        <v>1656</v>
       </c>
       <c r="E1" s="99" t="s">
-        <v>1623</v>
+        <v>1657</v>
       </c>
       <c r="F1" s="99" t="s">
-        <v>1624</v>
+        <v>1658</v>
       </c>
       <c r="G1" s="99" t="s">
-        <v>1625</v>
+        <v>1659</v>
       </c>
       <c r="H1" s="99" t="s">
-        <v>1626</v>
+        <v>1660</v>
       </c>
       <c r="I1" s="99" t="s">
-        <v>1627</v>
+        <v>1661</v>
       </c>
       <c r="J1" s="99" t="s">
-        <v>1628</v>
+        <v>1662</v>
       </c>
       <c r="K1" s="99" t="s">
-        <v>1629</v>
+        <v>1663</v>
       </c>
       <c r="L1" s="99" t="s">
-        <v>1630</v>
+        <v>1664</v>
       </c>
       <c r="M1" s="99" t="s">
-        <v>1631</v>
+        <v>1665</v>
       </c>
       <c r="N1" s="99" t="s">
-        <v>1632</v>
+        <v>1666</v>
       </c>
       <c r="O1" s="99" t="s">
-        <v>1633</v>
+        <v>1667</v>
       </c>
       <c r="P1" s="99" t="s">
-        <v>1634</v>
+        <v>1668</v>
       </c>
       <c r="Q1" s="99" t="s">
-        <v>1635</v>
+        <v>1669</v>
       </c>
       <c r="R1" s="99" t="s">
-        <v>1636</v>
+        <v>1670</v>
       </c>
       <c r="S1" s="99" t="s">
-        <v>1637</v>
+        <v>1671</v>
       </c>
       <c r="T1" s="99" t="s">
-        <v>1638</v>
+        <v>1672</v>
       </c>
       <c r="U1" s="99" t="s">
-        <v>1639</v>
+        <v>1673</v>
       </c>
       <c r="V1" s="99" t="s">
-        <v>1640</v>
+        <v>1674</v>
       </c>
       <c r="W1" s="99" t="s">
-        <v>1641</v>
+        <v>1675</v>
       </c>
       <c r="X1" s="99" t="s">
-        <v>1642</v>
+        <v>1676</v>
       </c>
       <c r="Y1" s="99" t="s">
-        <v>1643</v>
+        <v>1677</v>
       </c>
       <c r="Z1" s="99" t="s">
-        <v>1644</v>
+        <v>1678</v>
       </c>
       <c r="AA1" s="99" t="s">
-        <v>1645</v>
+        <v>1679</v>
       </c>
       <c r="AB1" s="99" t="s">
-        <v>1646</v>
+        <v>1680</v>
       </c>
       <c r="AC1" s="99" t="s">
-        <v>1647</v>
+        <v>1681</v>
       </c>
       <c r="AD1" s="19" t="s">
         <v>100</v>
@@ -40925,7 +41210,7 @@
         <v>58</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>1648</v>
+        <v>1682</v>
       </c>
       <c r="C2" s="0" t="s">
         <v>1255</v>
@@ -40937,10 +41222,10 @@
         <v>58</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>1649</v>
+        <v>1547</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="H2" s="0" t="s">
         <v>1218</v>
@@ -40952,7 +41237,7 @@
         <v>163</v>
       </c>
       <c r="K2" s="0" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="L2" s="0" t="s">
         <v>1024</v>
@@ -40961,28 +41246,28 @@
         <v>1259</v>
       </c>
       <c r="N2" s="0" t="s">
-        <v>1479</v>
+        <v>1485</v>
       </c>
       <c r="O2" s="0" t="s">
         <v>74</v>
       </c>
       <c r="P2" s="0" t="s">
-        <v>1432</v>
+        <v>1438</v>
       </c>
       <c r="Q2" s="0" t="s">
-        <v>1650</v>
+        <v>1683</v>
       </c>
       <c r="R2" s="0" t="s">
-        <v>1531</v>
+        <v>1566</v>
       </c>
       <c r="S2" s="0" t="s">
         <v>74</v>
       </c>
       <c r="T2" s="0" t="s">
-        <v>1536</v>
+        <v>1571</v>
       </c>
       <c r="U2" s="0" t="s">
-        <v>1651</v>
+        <v>1684</v>
       </c>
       <c r="V2" s="0" t="s">
         <v>1238</v>
@@ -40995,16 +41280,16 @@
         <v>100</v>
       </c>
       <c r="Y2" s="0" t="s">
-        <v>1565</v>
+        <v>1599</v>
       </c>
       <c r="Z2" s="0" t="s">
-        <v>1598</v>
+        <v>1632</v>
       </c>
       <c r="AA2" s="0" t="s">
-        <v>1652</v>
+        <v>1685</v>
       </c>
       <c r="AB2" s="0" t="s">
-        <v>1653</v>
+        <v>1686</v>
       </c>
       <c r="AC2" s="0" t="s">
         <v>128</v>
@@ -41027,10 +41312,10 @@
         <v>66</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>1654</v>
+        <v>1687</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>1383</v>
+        <v>1389</v>
       </c>
       <c r="H3" s="0" t="s">
         <v>1219</v>
@@ -41039,40 +41324,40 @@
         <v>75</v>
       </c>
       <c r="J3" s="0" t="s">
-        <v>1434</v>
+        <v>1440</v>
       </c>
       <c r="K3" s="0" t="s">
-        <v>1422</v>
+        <v>1428</v>
       </c>
       <c r="L3" s="0" t="s">
         <v>1027</v>
       </c>
       <c r="M3" s="0" t="s">
-        <v>1486</v>
+        <v>1492</v>
       </c>
       <c r="N3" s="0" t="s">
-        <v>1472</v>
+        <v>1478</v>
       </c>
       <c r="O3" s="0" t="s">
         <v>75</v>
       </c>
       <c r="P3" s="0" t="s">
-        <v>1655</v>
+        <v>1688</v>
       </c>
       <c r="Q3" s="0" t="s">
-        <v>1656</v>
+        <v>1689</v>
       </c>
       <c r="R3" s="0" t="s">
-        <v>1539</v>
+        <v>1508</v>
       </c>
       <c r="S3" s="0" t="s">
-        <v>1523</v>
+        <v>1558</v>
       </c>
       <c r="T3" s="0" t="s">
-        <v>1538</v>
+        <v>1573</v>
       </c>
       <c r="U3" s="0" t="s">
-        <v>1657</v>
+        <v>1690</v>
       </c>
       <c r="V3" s="0" t="s">
         <v>1241</v>
@@ -41085,16 +41370,16 @@
         <v>336</v>
       </c>
       <c r="Y3" s="0" t="s">
-        <v>1658</v>
+        <v>1691</v>
       </c>
       <c r="Z3" s="0" t="s">
-        <v>1599</v>
+        <v>1633</v>
       </c>
       <c r="AA3" s="0" t="s">
-        <v>1659</v>
+        <v>1692</v>
       </c>
       <c r="AB3" s="0" t="s">
-        <v>1660</v>
+        <v>1693</v>
       </c>
       <c r="AC3" s="0" t="s">
         <v>133</v>
@@ -41105,19 +41390,19 @@
         <v>67</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>1661</v>
+        <v>1694</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>1385</v>
+        <v>1391</v>
       </c>
       <c r="E4" s="0" t="s">
         <v>67</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>1662</v>
+        <v>1695</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>1386</v>
+        <v>1392</v>
       </c>
       <c r="H4" s="0" t="s">
         <v>1220</v>
@@ -41129,43 +41414,43 @@
         <v>165</v>
       </c>
       <c r="L4" s="0" t="s">
-        <v>1463</v>
+        <v>1469</v>
       </c>
       <c r="M4" s="0" t="s">
-        <v>1663</v>
+        <v>1696</v>
       </c>
       <c r="O4" s="0" t="s">
         <v>1259</v>
       </c>
       <c r="P4" s="0" t="s">
-        <v>1664</v>
+        <v>1697</v>
       </c>
       <c r="Q4" s="0" t="s">
-        <v>1665</v>
+        <v>1698</v>
       </c>
       <c r="R4" s="0" t="s">
-        <v>1545</v>
+        <v>1579</v>
       </c>
       <c r="S4" s="0" t="s">
-        <v>1524</v>
+        <v>1559</v>
       </c>
       <c r="T4" s="0" t="s">
         <v>75</v>
       </c>
       <c r="U4" s="0" t="s">
-        <v>1666</v>
+        <v>1699</v>
       </c>
       <c r="V4" s="0" t="s">
-        <v>1667</v>
+        <v>1700</v>
       </c>
       <c r="Z4" s="0" t="s">
-        <v>1668</v>
+        <v>1701</v>
       </c>
       <c r="AA4" s="0" t="s">
-        <v>1669</v>
+        <v>1702</v>
       </c>
       <c r="AB4" s="0" t="s">
-        <v>1670</v>
+        <v>1703</v>
       </c>
       <c r="AC4" s="0" t="s">
         <v>135</v>
@@ -41176,13 +41461,13 @@
         <v>161</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>1671</v>
+        <v>1704</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>1672</v>
+        <v>1705</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>1388</v>
+        <v>1394</v>
       </c>
       <c r="H5" s="0" t="s">
         <v>1221</v>
@@ -41191,37 +41476,37 @@
         <v>77</v>
       </c>
       <c r="J5" s="0" t="s">
-        <v>1436</v>
+        <v>1442</v>
       </c>
       <c r="L5" s="0" t="s">
-        <v>1469</v>
+        <v>1475</v>
       </c>
       <c r="O5" s="0" t="s">
-        <v>1673</v>
+        <v>1706</v>
       </c>
       <c r="P5" s="0" t="s">
-        <v>1674</v>
+        <v>1707</v>
       </c>
       <c r="Q5" s="0" t="s">
-        <v>1675</v>
+        <v>1708</v>
       </c>
       <c r="T5" s="0" t="s">
-        <v>1533</v>
+        <v>1568</v>
       </c>
       <c r="U5" s="0" t="s">
         <v>102</v>
       </c>
       <c r="V5" s="0" t="s">
-        <v>1676</v>
+        <v>1709</v>
       </c>
       <c r="Z5" s="0" t="s">
-        <v>1677</v>
+        <v>1710</v>
       </c>
       <c r="AA5" s="0" t="s">
-        <v>1666</v>
+        <v>1699</v>
       </c>
       <c r="AB5" s="0" t="s">
-        <v>1678</v>
+        <v>1711</v>
       </c>
       <c r="AC5" s="0" t="s">
         <v>137</v>
@@ -41235,7 +41520,7 @@
         <v>169</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>1390</v>
+        <v>1396</v>
       </c>
       <c r="H6" s="0" t="s">
         <v>1222</v>
@@ -41244,25 +41529,25 @@
         <v>78</v>
       </c>
       <c r="J6" s="0" t="s">
-        <v>1679</v>
+        <v>1712</v>
       </c>
       <c r="L6" s="0" t="s">
-        <v>1473</v>
+        <v>1479</v>
       </c>
       <c r="P6" s="0" t="s">
-        <v>1680</v>
+        <v>1713</v>
       </c>
       <c r="Q6" s="0" t="s">
-        <v>1681</v>
+        <v>1714</v>
       </c>
       <c r="Z6" s="0" t="s">
-        <v>1682</v>
+        <v>1715</v>
       </c>
       <c r="AA6" s="0" t="s">
-        <v>1663</v>
+        <v>1696</v>
       </c>
       <c r="AB6" s="0" t="s">
-        <v>1683</v>
+        <v>1716</v>
       </c>
       <c r="AC6" s="0" t="s">
         <v>139</v>
@@ -41273,7 +41558,7 @@
         <v>165</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>1392</v>
+        <v>1398</v>
       </c>
       <c r="H7" s="0" t="s">
         <v>1223</v>
@@ -41282,16 +41567,16 @@
         <v>79</v>
       </c>
       <c r="J7" s="0" t="s">
-        <v>1684</v>
+        <v>1717</v>
       </c>
       <c r="L7" s="0" t="s">
-        <v>1476</v>
+        <v>1482</v>
       </c>
       <c r="Z7" s="0" t="s">
-        <v>1685</v>
+        <v>1718</v>
       </c>
       <c r="AB7" s="0" t="s">
-        <v>1686</v>
+        <v>1719</v>
       </c>
       <c r="AC7" s="0" t="s">
         <v>141</v>
@@ -41302,22 +41587,22 @@
         <v>167</v>
       </c>
       <c r="G8" s="0" t="s">
-        <v>1393</v>
+        <v>1399</v>
       </c>
       <c r="H8" s="0" t="s">
         <v>1025</v>
       </c>
       <c r="J8" s="0" t="s">
-        <v>1687</v>
+        <v>1720</v>
       </c>
       <c r="L8" s="0" t="s">
-        <v>1480</v>
+        <v>1486</v>
       </c>
       <c r="Z8" s="0" t="s">
-        <v>1688</v>
+        <v>1721</v>
       </c>
       <c r="AB8" s="0" t="s">
-        <v>1689</v>
+        <v>1722</v>
       </c>
       <c r="AC8" s="0" t="s">
         <v>143</v>
@@ -41334,7 +41619,7 @@
         <v>1025</v>
       </c>
       <c r="L9" s="0" t="s">
-        <v>1482</v>
+        <v>1488</v>
       </c>
       <c r="AB9" s="0" t="s">
         <v>92</v>
@@ -41348,13 +41633,13 @@
         <v>1225</v>
       </c>
       <c r="J10" s="0" t="s">
-        <v>1690</v>
+        <v>1723</v>
       </c>
       <c r="L10" s="0" t="s">
         <v>169</v>
       </c>
       <c r="AB10" s="0" t="s">
-        <v>1691</v>
+        <v>1724</v>
       </c>
       <c r="AC10" s="0" t="s">
         <v>147</v>
@@ -41365,10 +41650,10 @@
         <v>1226</v>
       </c>
       <c r="J11" s="0" t="s">
-        <v>1692</v>
+        <v>1725</v>
       </c>
       <c r="AB11" s="0" t="s">
-        <v>1693</v>
+        <v>1726</v>
       </c>
       <c r="AC11" s="0" t="s">
         <v>149</v>
@@ -41382,7 +41667,7 @@
         <v>169</v>
       </c>
       <c r="AB12" s="0" t="s">
-        <v>1694</v>
+        <v>1727</v>
       </c>
       <c r="AC12" s="0" t="s">
         <v>151</v>
@@ -41393,7 +41678,7 @@
         <v>1228</v>
       </c>
       <c r="AB13" s="0" t="s">
-        <v>1695</v>
+        <v>1728</v>
       </c>
       <c r="AC13" s="0" t="s">
         <v>153</v>
